--- a/tame_output/ON/bt/strategyON_20240422.xlsx
+++ b/tame_output/ON/bt/strategyON_20240422.xlsx
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-199.9%</t>
+          <t>-200.0%</t>
         </is>
       </c>
     </row>
@@ -46194,16 +46194,16 @@
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.125094515757244</v>
+        <v>-4.125746685127993</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.109083904618141</v>
+        <v>1.108823036869842</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4976609607446779</v>
+        <v>-0.4983131301154269</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.46088155878798</v>
+        <v>2.46049025716553</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240422.xlsx
+++ b/tame_output/ON/bt/strategyON_20240422.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.3%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.5%</t>
+          <t>788.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.1%</t>
+          <t>-564.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-265.3%</t>
+          <t>-261.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.2%</t>
+          <t>-158.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.8%</t>
+          <t>-264.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-200.0%</t>
+          <t>-194.2%</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.31039034660745</v>
+        <v>-9.216442860307177</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.576579323954288</v>
+        <v>-0.5390003294341792</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.760934233845341</v>
+        <v>-2.666986747545067</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.491372698695235</v>
+        <v>1.547741190475399</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.076909124377853</v>
+        <v>-8.98296163807758</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4752624062245969</v>
+        <v>-0.4376834117044877</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.527453011615742</v>
+        <v>-2.433505525315469</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.639385860870847</v>
+        <v>1.695754352651011</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.897200594233979</v>
+        <v>-8.803253107933706</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4062712044800065</v>
+        <v>-0.3686922099598973</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.470281507453046</v>
+        <v>-2.376334021152772</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.670796553055505</v>
+        <v>1.727165044835669</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.764925120603092</v>
+        <v>-8.670977634302819</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3579935282806246</v>
+        <v>-0.3204145337605153</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.33800603382216</v>
+        <v>-2.244058547521886</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.745529323981064</v>
+        <v>1.801897815761228</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.574325445929938</v>
+        <v>-8.480377959629665</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2789385977237266</v>
+        <v>-0.2413596032036174</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.147406359149007</v>
+        <v>-2.053458872848733</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.862704189472592</v>
+        <v>1.919072681252756</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.325325647246357</v>
+        <v>-8.231378160946084</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1664323370266354</v>
+        <v>-0.1288533425065261</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.147406359149007</v>
+        <v>-2.053458872848733</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.875610530696251</v>
+        <v>1.931979022476416</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.430915637019462</v>
+        <v>-8.336968150719189</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3366442625350956</v>
+        <v>-0.2990652680149868</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.252996348922112</v>
+        <v>-2.159048862621838</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.68428060723317</v>
+        <v>1.740649099013334</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.449650539138059</v>
+        <v>-8.355703052837786</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2955938815054484</v>
+        <v>-0.2580148869853391</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.252996348922112</v>
+        <v>-2.159048862621838</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.732824949110256</v>
+        <v>1.78919344089042</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.301710497730459</v>
+        <v>-8.207763011430186</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3562967876305763</v>
+        <v>-0.318717793110467</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.232675433013554</v>
+        <v>-2.13872794671328</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.625138575967223</v>
+        <v>1.681507067747387</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.174818091295389</v>
+        <v>-8.080870604995116</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3142538113100262</v>
+        <v>-0.2766748167899169</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.105783026578484</v>
+        <v>-2.01183554027821</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.692560033574787</v>
+        <v>1.748928525354951</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.131269684524698</v>
+        <v>-8.037322198224425</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3037950606968427</v>
+        <v>-0.2662160661767334</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.105783026578484</v>
+        <v>-2.01183554027821</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.685599421479694</v>
+        <v>1.741967913259858</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.88912129107084</v>
+        <v>-7.795173804770567</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1924733489341564</v>
+        <v>-0.1548943544140471</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.105783026578484</v>
+        <v>-2.01183554027821</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.700061775860837</v>
+        <v>1.756430267641001</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.825891919302491</v>
+        <v>-7.731944433002218</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1726494797676219</v>
+        <v>-0.1350704852475131</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.105783026578484</v>
+        <v>-2.01183554027821</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.694593896320032</v>
+        <v>1.750962388100196</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.639404226925485</v>
+        <v>-7.545456740625212</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1005563088062429</v>
+        <v>-0.06297731428613362</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.919295334201478</v>
+        <v>-1.825347847901204</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.803984605756812</v>
+        <v>1.860353097536977</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.618255028022042</v>
+        <v>-7.524307541721769</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.0843956510075401</v>
+        <v>-0.04681665648743127</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.898146135298034</v>
+        <v>-1.804198648997761</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.824375103336203</v>
+        <v>1.880743595116368</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.374489586038598</v>
+        <v>-7.280542099738325</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.008891234132887949</v>
+        <v>0.04647022865299721</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.898146135298034</v>
+        <v>-1.804198648997761</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.820155811683254</v>
+        <v>1.876524303463418</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.110461518845337</v>
+        <v>-7.016514032545064</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1166267749302081</v>
+        <v>0.1542057694503174</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.696280736482081</v>
+        <v>-1.602333250181807</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.943399364892842</v>
+        <v>1.999767856673007</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.860611124896263</v>
+        <v>-6.76666363859599</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2093090074935402</v>
+        <v>0.2468880020136495</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.696280736482081</v>
+        <v>-1.602333250181807</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.936141439876544</v>
+        <v>1.992509931656709</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.557043635892284</v>
+        <v>-6.463096149592011</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3343351266157804</v>
+        <v>0.3719141211358896</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.696280736482081</v>
+        <v>-1.602333250181807</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.939740563397193</v>
+        <v>1.996109055177357</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.48356372704027</v>
+        <v>-6.389616240739997</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3770545962111398</v>
+        <v>0.4146335907312491</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.622800827630067</v>
+        <v>-1.528853341329793</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.997156014762956</v>
+        <v>2.05352450654312</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.258530727371447</v>
+        <v>-6.164583241071174</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4660882736949659</v>
+        <v>0.5036672682150751</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.397767827961244</v>
+        <v>-1.30382034166097</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.131196292180547</v>
+        <v>2.187564783960711</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.04389634973504</v>
+        <v>-5.949948863434767</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5566368258038459</v>
+        <v>0.5942158203239551</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.183133450324837</v>
+        <v>-1.089185964024563</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.264671719816707</v>
+        <v>2.321040211596872</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.777295992760688</v>
+        <v>-5.683348506460415</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6444712273773825</v>
+        <v>0.6820502218974918</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.183133450324837</v>
+        <v>-1.089185964024563</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.245865978600503</v>
+        <v>2.302234470380668</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.536865495955828</v>
+        <v>-5.442918009655555</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7423865027242038</v>
+        <v>0.7799654972443131</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9427029535199765</v>
+        <v>-0.8487554672197026</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.391867353308297</v>
+        <v>2.448235845088461</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.294074688306383</v>
+        <v>-5.20012720200611</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8434321396188023</v>
+        <v>0.8810111341389115</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9427029535199765</v>
+        <v>-0.8487554672197026</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.395796667143117</v>
+        <v>2.452165158923282</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.178134838681197</v>
+        <v>-5.084187352380924</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8904866633862163</v>
+        <v>0.9280656579063256</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8658812225038526</v>
+        <v>-0.7719337362035787</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.442568289670132</v>
+        <v>2.498936781450296</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.935479250258034</v>
+        <v>-4.841531763957761</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9845469699754754</v>
+        <v>1.022125964495584</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8658812225038526</v>
+        <v>-0.7719337362035787</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.439566360890125</v>
+        <v>2.495934852670289</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.715458452221023</v>
+        <v>-4.62151096592075</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.074134326200894</v>
+        <v>1.111713320721003</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7246613774358723</v>
+        <v>-0.6307138911355985</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.525877304941527</v>
+        <v>2.582245796721692</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.516209822316214</v>
+        <v>-4.422262336015941</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169727960964641</v>
+        <v>1.20730695548475</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7246613774358723</v>
+        <v>-0.6307138911355985</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.54177148774335</v>
+        <v>2.598139979523514</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.356694718796844</v>
+        <v>-4.262747232496571</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.23467984681269</v>
+        <v>1.2722588413328</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5651462739165024</v>
+        <v>-0.4711987876162286</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.638626394295274</v>
+        <v>2.694994886075439</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.212022573697107</v>
+        <v>-4.118075087396834</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.302636807414025</v>
+        <v>1.340215801934134</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.420474128816765</v>
+        <v>-0.3265266425164912</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.735517783916557</v>
+        <v>2.791886275696721</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.194253114766151</v>
+        <v>-4.100305628465878</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.225084283073129</v>
+        <v>1.262663277593238</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4027046698858094</v>
+        <v>-0.3087571835855356</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.661519151361852</v>
+        <v>2.717887643142016</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.107453616987142</v>
+        <v>-4.013506130686869</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.282204575507299</v>
+        <v>1.319783570027408</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4027046698858094</v>
+        <v>-0.3087571835855356</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.683919644684418</v>
+        <v>2.740288136464582</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.00776100225813</v>
+        <v>-3.913813515957857</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.322154022772316</v>
+        <v>1.359733017292425</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3030120551567977</v>
+        <v>-0.2090645688565239</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.743807614895237</v>
+        <v>2.800176106675401</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.07613118858214</v>
+        <v>-3.982183702281867</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.305812870717414</v>
+        <v>1.343391865237523</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.760379956791668</v>
+        <v>2.816748448571832</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.954714758955664</v>
+        <v>-3.86076727265539</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.344816151199896</v>
+        <v>1.382395145720005</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.750816665423559</v>
+        <v>2.807185157203723</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.985707918284369</v>
+        <v>-3.891760431984096</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.1571284525088</v>
+        <v>1.19470744702891</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.575526230463946</v>
+        <v>2.63189472224411</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.8102336584919</v>
+        <v>-3.716286172191626</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.231885388417576</v>
+        <v>1.269464382937685</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.580093462455734</v>
+        <v>2.636461954235898</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.921169911133148</v>
+        <v>-3.827222424832875</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.187522361247874</v>
+        <v>1.225101355767983</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.580104936342531</v>
+        <v>2.636473428122696</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.861414625799806</v>
+        <v>3.826030251913719</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.125746685127993</v>
+        <v>-4.030249002376109</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.108823036869842</v>
+        <v>1.147022109970596</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4983131301154269</v>
+        <v>-0.4028154473635423</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.46049025716553</v>
+        <v>2.517788866816661</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240422.xlsx
+++ b/tame_output/ON/bt/strategyON_20240422.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>116.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.7%</t>
+          <t>783.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-564.6%</t>
+          <t>-582.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-261.5%</t>
+          <t>-268.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.9%</t>
+          <t>-161.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-264.3%</t>
+          <t>-273.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-194.2%</t>
+          <t>-199.9%</t>
         </is>
       </c>
     </row>
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.216442860307177</v>
+        <v>-9.31039034660745</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5390003294341792</v>
+        <v>-0.576579323954288</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.666986747545067</v>
+        <v>-2.760934233845341</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.547741190475399</v>
+        <v>1.491372698695235</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.98296163807758</v>
+        <v>-9.076909124377853</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4376834117044877</v>
+        <v>-0.4752624062245969</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.433505525315469</v>
+        <v>-2.527453011615742</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.695754352651011</v>
+        <v>1.639385860870847</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.803253107933706</v>
+        <v>-8.897200594233979</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3686922099598973</v>
+        <v>-0.4062712044800065</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.376334021152772</v>
+        <v>-2.470281507453046</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.727165044835669</v>
+        <v>1.670796553055505</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.670977634302819</v>
+        <v>-8.764925120603092</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3204145337605153</v>
+        <v>-0.3579935282806246</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.244058547521886</v>
+        <v>-2.33800603382216</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.801897815761228</v>
+        <v>1.745529323981064</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.480377959629665</v>
+        <v>-8.574325445929938</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2413596032036174</v>
+        <v>-0.2789385977237266</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.053458872848733</v>
+        <v>-2.147406359149007</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.919072681252756</v>
+        <v>1.862704189472592</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.231378160946084</v>
+        <v>-8.325325647246357</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1288533425065261</v>
+        <v>-0.1664323370266354</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.053458872848733</v>
+        <v>-2.147406359149007</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.931979022476416</v>
+        <v>1.875610530696251</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.336968150719189</v>
+        <v>-8.430915637019462</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2990652680149868</v>
+        <v>-0.3366442625350956</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.159048862621838</v>
+        <v>-2.252996348922112</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.740649099013334</v>
+        <v>1.68428060723317</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.355703052837786</v>
+        <v>-8.449650539138059</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2580148869853391</v>
+        <v>-0.2955938815054484</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.159048862621838</v>
+        <v>-2.252996348922112</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.78919344089042</v>
+        <v>1.732824949110256</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.207763011430186</v>
+        <v>-8.301710497730459</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.318717793110467</v>
+        <v>-0.3562967876305763</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.13872794671328</v>
+        <v>-2.232675433013554</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.681507067747387</v>
+        <v>1.625138575967223</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.080870604995116</v>
+        <v>-8.174818091295389</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2766748167899169</v>
+        <v>-0.3142538113100262</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.01183554027821</v>
+        <v>-2.105783026578484</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.748928525354951</v>
+        <v>1.692560033574787</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.037322198224425</v>
+        <v>-8.131269684524698</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2662160661767334</v>
+        <v>-0.3037950606968427</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.01183554027821</v>
+        <v>-2.105783026578484</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.741967913259858</v>
+        <v>1.685599421479694</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.795173804770567</v>
+        <v>-7.88912129107084</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1548943544140471</v>
+        <v>-0.1924733489341564</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.01183554027821</v>
+        <v>-2.105783026578484</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.756430267641001</v>
+        <v>1.700061775860837</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.731944433002218</v>
+        <v>-7.825891919302491</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1350704852475131</v>
+        <v>-0.1726494797676219</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.01183554027821</v>
+        <v>-2.105783026578484</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.750962388100196</v>
+        <v>1.694593896320032</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.545456740625212</v>
+        <v>-7.639404226925485</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.06297731428613362</v>
+        <v>-0.1005563088062429</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.825347847901204</v>
+        <v>-1.919295334201478</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.860353097536977</v>
+        <v>1.803984605756812</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.524307541721769</v>
+        <v>-7.618255028022042</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.04681665648743127</v>
+        <v>-0.0843956510075401</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.804198648997761</v>
+        <v>-1.898146135298034</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.880743595116368</v>
+        <v>1.824375103336203</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.280542099738325</v>
+        <v>-7.374489586038598</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.04647022865299721</v>
+        <v>0.008891234132887949</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.804198648997761</v>
+        <v>-1.898146135298034</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.876524303463418</v>
+        <v>1.820155811683254</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.016514032545064</v>
+        <v>-7.110461518845337</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1542057694503174</v>
+        <v>0.1166267749302081</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.602333250181807</v>
+        <v>-1.696280736482081</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.999767856673007</v>
+        <v>1.943399364892842</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.76666363859599</v>
+        <v>-6.860611124896263</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2468880020136495</v>
+        <v>0.2093090074935402</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.602333250181807</v>
+        <v>-1.696280736482081</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.992509931656709</v>
+        <v>1.936141439876544</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.463096149592011</v>
+        <v>-6.557043635892284</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3719141211358896</v>
+        <v>0.3343351266157804</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.602333250181807</v>
+        <v>-1.696280736482081</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.996109055177357</v>
+        <v>1.939740563397193</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.389616240739997</v>
+        <v>-6.48356372704027</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4146335907312491</v>
+        <v>0.3770545962111398</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.528853341329793</v>
+        <v>-1.622800827630067</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.05352450654312</v>
+        <v>1.997156014762956</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.164583241071174</v>
+        <v>-6.258530727371447</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5036672682150751</v>
+        <v>0.4660882736949659</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.30382034166097</v>
+        <v>-1.397767827961244</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.187564783960711</v>
+        <v>2.131196292180547</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.949948863434767</v>
+        <v>-6.04389634973504</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5942158203239551</v>
+        <v>0.5566368258038459</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.089185964024563</v>
+        <v>-1.183133450324837</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.321040211596872</v>
+        <v>2.264671719816707</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.683348506460415</v>
+        <v>-5.777295992760688</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6820502218974918</v>
+        <v>0.6444712273773825</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.089185964024563</v>
+        <v>-1.183133450324837</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.302234470380668</v>
+        <v>2.245865978600503</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.442918009655555</v>
+        <v>-5.536865495955828</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7799654972443131</v>
+        <v>0.7423865027242038</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8487554672197026</v>
+        <v>-0.9427029535199765</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.448235845088461</v>
+        <v>2.391867353308297</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.20012720200611</v>
+        <v>-5.294074688306383</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8810111341389115</v>
+        <v>0.8434321396188023</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8487554672197026</v>
+        <v>-0.9427029535199765</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.452165158923282</v>
+        <v>2.395796667143117</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.084187352380924</v>
+        <v>-5.178134838681197</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9280656579063256</v>
+        <v>0.8904866633862163</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7719337362035787</v>
+        <v>-0.8658812225038526</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.498936781450296</v>
+        <v>2.442568289670132</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.841531763957761</v>
+        <v>-4.935479250258034</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.022125964495584</v>
+        <v>0.9845469699754754</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7719337362035787</v>
+        <v>-0.8658812225038526</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.495934852670289</v>
+        <v>2.439566360890125</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.62151096592075</v>
+        <v>-4.715458452221023</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.111713320721003</v>
+        <v>1.074134326200894</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6307138911355985</v>
+        <v>-0.7246613774358723</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.582245796721692</v>
+        <v>2.525877304941527</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.422262336015941</v>
+        <v>-4.598839129931144</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.20730695548475</v>
+        <v>1.136676237918669</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6307138911355985</v>
+        <v>-0.7246613774358723</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.598139979523514</v>
+        <v>2.54177148774335</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.262747232496571</v>
+        <v>-4.439324026411774</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.2722588413328</v>
+        <v>1.201628123766719</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4711987876162286</v>
+        <v>-0.5651462739165024</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.694994886075439</v>
+        <v>2.638626394295274</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.118075087396834</v>
+        <v>-4.294651881312037</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.340215801934134</v>
+        <v>1.269585084368053</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3265266425164912</v>
+        <v>-0.420474128816765</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.791886275696721</v>
+        <v>2.735517783916557</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.100305628465878</v>
+        <v>-4.276882422381081</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.262663277593238</v>
+        <v>1.192032560027157</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3087571835855356</v>
+        <v>-0.4027046698858094</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.717887643142016</v>
+        <v>2.661519151361852</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.013506130686869</v>
+        <v>-4.190082924602072</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.319783570027408</v>
+        <v>1.249152852461327</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3087571835855356</v>
+        <v>-0.4027046698858094</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.740288136464582</v>
+        <v>2.683919644684418</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.913813515957857</v>
+        <v>-4.09039030987306</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.359733017292425</v>
+        <v>1.289102299726344</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2090645688565239</v>
+        <v>-0.3030120551567977</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.800176106675401</v>
+        <v>2.743807614895237</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.982183702281867</v>
+        <v>-4.15876049619707</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.343391865237523</v>
+        <v>1.272761147671442</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1997888698203089</v>
+        <v>-0.2937363561205827</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.816748448571832</v>
+        <v>2.760379956791668</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.86076727265539</v>
+        <v>-4.037344066570594</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.382395145720005</v>
+        <v>1.311764428153924</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1997888698203089</v>
+        <v>-0.2937363561205827</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.807185157203723</v>
+        <v>2.750816665423559</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.891760431984096</v>
+        <v>-4.068337225899299</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.19470744702891</v>
+        <v>1.124076729462828</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1997888698203089</v>
+        <v>-0.2937363561205827</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.63189472224411</v>
+        <v>2.575526230463946</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.716286172191626</v>
+        <v>-3.89286296610683</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.269464382937685</v>
+        <v>1.198833665371604</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1997888698203089</v>
+        <v>-0.2937363561205827</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.636461954235898</v>
+        <v>2.580093462455734</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.827222424832875</v>
+        <v>-4.003799218748078</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.225101355767983</v>
+        <v>1.154470638201902</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1997888698203089</v>
+        <v>-0.2937363561205827</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.636473428122696</v>
+        <v>2.580104936342531</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.826030251913719</v>
+        <v>3.559790765376891</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.030249002376109</v>
+        <v>-4.206825796291311</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.147022109970596</v>
+        <v>1.076391392404514</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4028154473635423</v>
+        <v>-0.4967629336638161</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.517788866816661</v>
+        <v>2.461420375036497</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240422.xlsx
+++ b/tame_output/ON/bt/strategyON_20240422.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>58.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-16.4%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.1%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.1%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>783.7%</t>
+          <t>788.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-582.3%</t>
+          <t>-553.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-268.6%</t>
+          <t>-257.0%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.4%</t>
+          <t>-163.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.7%</t>
+          <t>-253.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-199.9%</t>
+          <t>-151.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1941"/>
+  <dimension ref="A1:G1942"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.598839129931144</v>
+        <v>-4.516209822316214</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.136676237918669</v>
+        <v>1.169727960964641</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7246613774358723</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.439324026411774</v>
+        <v>-4.356694718796844</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.201628123766719</v>
+        <v>1.23467984681269</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5651462739165024</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.294651881312037</v>
+        <v>-4.212022573697107</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.269585084368053</v>
+        <v>1.302636807414025</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.420474128816765</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.276882422381081</v>
+        <v>-4.194253114766151</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.192032560027157</v>
+        <v>1.225084283073129</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4027046698858094</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.190082924602072</v>
+        <v>-4.107453616987142</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.249152852461327</v>
+        <v>1.282204575507299</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4027046698858094</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.09039030987306</v>
+        <v>-4.00776100225813</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.289102299726344</v>
+        <v>1.322154022772316</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3030120551567977</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.15876049619707</v>
+        <v>-4.07613118858214</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.272761147671442</v>
+        <v>1.305812870717414</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.2937363561205827</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.037344066570594</v>
+        <v>-3.954714758955664</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.311764428153924</v>
+        <v>1.344816151199896</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.2937363561205827</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.068337225899299</v>
+        <v>-3.985707918284369</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.124076729462828</v>
+        <v>1.1571284525088</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.2937363561205827</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.89286296610683</v>
+        <v>-3.8102336584919</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.198833665371604</v>
+        <v>1.231885388417576</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.2937363561205827</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.003799218748078</v>
+        <v>-3.921169911133148</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.154470638201902</v>
+        <v>1.187522361247874</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.2937363561205827</v>
@@ -46188,22 +46188,45 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.559790765376891</v>
+        <v>3.773206721581284</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.206825796291311</v>
+        <v>-3.917893149633295</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.076391392404514</v>
+        <v>1.191964451067721</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4967629336638161</v>
+        <v>-0.29045959462073</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.461420375036497</v>
+        <v>2.585202378462348</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="B1942" t="n">
+        <v>3.860698421032866</v>
+      </c>
+      <c r="C1942" t="n">
+        <v>2.952613472414173</v>
+      </c>
+      <c r="D1942" t="n">
+        <v>-3.917893149633295</v>
+      </c>
+      <c r="E1942" t="n">
+        <v>1.191964451067721</v>
+      </c>
+      <c r="F1942" t="n">
+        <v>-0.29045959462073</v>
+      </c>
+      <c r="G1942" t="n">
+        <v>2.945677269400541</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240422.xlsx
+++ b/tame_output/ON/bt/strategyON_20240422.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,25 +811,25 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-48.0%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.9%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>136.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.5%</t>
+          <t>783.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-553.4%</t>
+          <t>-574.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-257.0%</t>
+          <t>-265.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-163.2%</t>
+          <t>-159.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-253.0%</t>
+          <t>-264.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-151.5%</t>
+          <t>-183.0%</t>
         </is>
       </c>
     </row>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.31039034660745</v>
+        <v>-9.216442860307177</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.576579323954288</v>
+        <v>-0.5390003294341792</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.760934233845341</v>
+        <v>-2.666986747545067</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.491372698695235</v>
+        <v>1.547741190475399</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.076909124377853</v>
+        <v>-8.98296163807758</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4752624062245969</v>
+        <v>-0.4376834117044877</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.527453011615742</v>
+        <v>-2.433505525315469</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.639385860870847</v>
+        <v>1.695754352651011</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.897200594233979</v>
+        <v>-8.803253107933706</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4062712044800065</v>
+        <v>-0.3686922099598973</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.470281507453046</v>
+        <v>-2.376334021152772</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.670796553055505</v>
+        <v>1.727165044835669</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.764925120603092</v>
+        <v>-8.670977634302819</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3579935282806246</v>
+        <v>-0.3204145337605153</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.33800603382216</v>
+        <v>-2.244058547521886</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.745529323981064</v>
+        <v>1.801897815761228</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.574325445929938</v>
+        <v>-8.480377959629665</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2789385977237266</v>
+        <v>-0.2413596032036174</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.147406359149007</v>
+        <v>-2.053458872848733</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.862704189472592</v>
+        <v>1.919072681252756</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.325325647246357</v>
+        <v>-8.231378160946084</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1664323370266354</v>
+        <v>-0.1288533425065261</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.147406359149007</v>
+        <v>-2.053458872848733</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.875610530696251</v>
+        <v>1.931979022476416</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.430915637019462</v>
+        <v>-8.336968150719189</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3366442625350956</v>
+        <v>-0.2990652680149868</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.252996348922112</v>
+        <v>-2.159048862621838</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.68428060723317</v>
+        <v>1.740649099013334</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.449650539138059</v>
+        <v>-8.355703052837786</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2955938815054484</v>
+        <v>-0.2580148869853391</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.252996348922112</v>
+        <v>-2.159048862621838</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.732824949110256</v>
+        <v>1.78919344089042</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.301710497730459</v>
+        <v>-8.207763011430186</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3562967876305763</v>
+        <v>-0.318717793110467</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.232675433013554</v>
+        <v>-2.13872794671328</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.625138575967223</v>
+        <v>1.681507067747387</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.174818091295389</v>
+        <v>-8.080870604995116</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3142538113100262</v>
+        <v>-0.2766748167899169</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.105783026578484</v>
+        <v>-2.01183554027821</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.692560033574787</v>
+        <v>1.748928525354951</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.131269684524698</v>
+        <v>-8.037322198224425</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3037950606968427</v>
+        <v>-0.2662160661767334</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.105783026578484</v>
+        <v>-2.01183554027821</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.685599421479694</v>
+        <v>1.741967913259858</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.88912129107084</v>
+        <v>-7.795173804770567</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1924733489341564</v>
+        <v>-0.1548943544140471</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.105783026578484</v>
+        <v>-2.01183554027821</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.700061775860837</v>
+        <v>1.756430267641001</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.825891919302491</v>
+        <v>-7.731944433002218</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1726494797676219</v>
+        <v>-0.1350704852475131</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.105783026578484</v>
+        <v>-2.01183554027821</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.694593896320032</v>
+        <v>1.750962388100196</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.639404226925485</v>
+        <v>-7.545456740625212</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1005563088062429</v>
+        <v>-0.06297731428613362</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.919295334201478</v>
+        <v>-1.825347847901204</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.803984605756812</v>
+        <v>1.860353097536977</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.618255028022042</v>
+        <v>-7.524307541721769</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.0843956510075401</v>
+        <v>-0.04681665648743127</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.898146135298034</v>
+        <v>-1.804198648997761</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.824375103336203</v>
+        <v>1.880743595116368</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.374489586038598</v>
+        <v>-7.280542099738325</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.008891234132887949</v>
+        <v>0.04647022865299721</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.898146135298034</v>
+        <v>-1.804198648997761</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.820155811683254</v>
+        <v>1.876524303463418</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.110461518845337</v>
+        <v>-7.016514032545064</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1166267749302081</v>
+        <v>0.1542057694503174</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.696280736482081</v>
+        <v>-1.602333250181807</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.943399364892842</v>
+        <v>1.999767856673007</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.860611124896263</v>
+        <v>-6.76666363859599</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2093090074935402</v>
+        <v>0.2468880020136495</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.696280736482081</v>
+        <v>-1.602333250181807</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.936141439876544</v>
+        <v>1.992509931656709</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.557043635892284</v>
+        <v>-6.463096149592011</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3343351266157804</v>
+        <v>0.3719141211358896</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.696280736482081</v>
+        <v>-1.602333250181807</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.939740563397193</v>
+        <v>1.996109055177357</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.48356372704027</v>
+        <v>-6.389616240739997</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3770545962111398</v>
+        <v>0.4146335907312491</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.622800827630067</v>
+        <v>-1.528853341329793</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.997156014762956</v>
+        <v>2.05352450654312</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.258530727371447</v>
+        <v>-6.164583241071174</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4660882736949659</v>
+        <v>0.5036672682150751</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.397767827961244</v>
+        <v>-1.30382034166097</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.131196292180547</v>
+        <v>2.187564783960711</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.04389634973504</v>
+        <v>-5.949948863434767</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5566368258038459</v>
+        <v>0.5942158203239551</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.183133450324837</v>
+        <v>-1.089185964024563</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.264671719816707</v>
+        <v>2.321040211596872</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.777295992760688</v>
+        <v>-5.683348506460415</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6444712273773825</v>
+        <v>0.6820502218974918</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.183133450324837</v>
+        <v>-1.089185964024563</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.245865978600503</v>
+        <v>2.302234470380668</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.536865495955828</v>
+        <v>-5.442918009655555</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7423865027242038</v>
+        <v>0.7799654972443131</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9427029535199765</v>
+        <v>-0.8487554672197026</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.391867353308297</v>
+        <v>2.448235845088461</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.294074688306383</v>
+        <v>-5.20012720200611</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8434321396188023</v>
+        <v>0.8810111341389115</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9427029535199765</v>
+        <v>-0.8487554672197026</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.395796667143117</v>
+        <v>2.452165158923282</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.178134838681197</v>
+        <v>-5.084187352380924</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8904866633862163</v>
+        <v>0.9280656579063256</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8658812225038526</v>
+        <v>-0.7719337362035787</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.442568289670132</v>
+        <v>2.498936781450296</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.935479250258034</v>
+        <v>-4.841531763957761</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9845469699754754</v>
+        <v>1.022125964495584</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8658812225038526</v>
+        <v>-0.7719337362035787</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.439566360890125</v>
+        <v>2.495934852670289</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.715458452221023</v>
+        <v>-4.62151096592075</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.074134326200894</v>
+        <v>1.111713320721003</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7246613774358723</v>
+        <v>-0.6307138911355985</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.525877304941527</v>
+        <v>2.582245796721692</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.516209822316214</v>
+        <v>-4.521051165760024</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169727960964641</v>
+        <v>1.167791423587117</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7246613774358723</v>
+        <v>-0.6307138911355985</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.54177148774335</v>
+        <v>2.598139979523514</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.356694718796844</v>
+        <v>-4.361536062240654</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.23467984681269</v>
+        <v>1.232743309435166</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5651462739165024</v>
+        <v>-0.4711987876162286</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.638626394295274</v>
+        <v>2.694994886075439</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.212022573697107</v>
+        <v>-4.216863917140917</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.302636807414025</v>
+        <v>1.300700270036501</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.420474128816765</v>
+        <v>-0.3265266425164912</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.735517783916557</v>
+        <v>2.791886275696721</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.194253114766151</v>
+        <v>-4.199094458209961</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.225084283073129</v>
+        <v>1.223147745695605</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4027046698858094</v>
+        <v>-0.3087571835855356</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.661519151361852</v>
+        <v>2.717887643142016</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.107453616987142</v>
+        <v>-4.112294960430953</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.282204575507299</v>
+        <v>1.280268038129775</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4027046698858094</v>
+        <v>-0.3087571835855356</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.683919644684418</v>
+        <v>2.740288136464582</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.00776100225813</v>
+        <v>-4.012602345701941</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.322154022772316</v>
+        <v>1.320217485394791</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3030120551567977</v>
+        <v>-0.2090645688565239</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.743807614895237</v>
+        <v>2.800176106675401</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.07613118858214</v>
+        <v>-4.080972532025951</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.305812870717414</v>
+        <v>1.303876333339889</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.760379956791668</v>
+        <v>2.816748448571832</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.954714758955664</v>
+        <v>-3.959556102399475</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.344816151199896</v>
+        <v>1.342879613822371</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.750816665423559</v>
+        <v>2.807185157203723</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.985707918284369</v>
+        <v>-3.99054926172818</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.1571284525088</v>
+        <v>1.155191915131276</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.575526230463946</v>
+        <v>2.63189472224411</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.8102336584919</v>
+        <v>-3.815075001935711</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.231885388417576</v>
+        <v>1.229948851040051</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.580093462455734</v>
+        <v>2.636461954235898</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.921169911133148</v>
+        <v>-3.926011254576959</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.187522361247874</v>
+        <v>1.18558582387035</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2937363561205827</v>
+        <v>-0.1997888698203089</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.580104936342531</v>
+        <v>2.636473428122696</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581284</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.917893149633295</v>
+        <v>-4.129037832120193</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.191964451067721</v>
+        <v>1.107506578072962</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.29045959462073</v>
+        <v>-0.4028154473635423</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.585202378462348</v>
+        <v>2.517788866816661</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.860698421032866</v>
+        <v>3.561523597899424</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.952613472414173</v>
+        <v>2.636724498191444</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.917893149633295</v>
+        <v>-4.129037832120193</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.191964451067721</v>
+        <v>1.107506578072962</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.29045959462073</v>
+        <v>-0.4028154473635423</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.945677269400541</v>
+        <v>2.629788295177812</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240422.xlsx
+++ b/tame_output/ON/bt/strategyON_20240422.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,35 +811,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.0%</t>
+          <t>134.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-685.6%</t>
+          <t>-669.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.6%</t>
+          <t>-55.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>783.7%</t>
+          <t>788.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.5%</t>
+          <t>-541.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.9%</t>
+          <t>-268.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-43.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-45.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-265.5%</t>
+          <t>-252.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.0%</t>
+          <t>-153.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-264.3%</t>
+          <t>-241.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-183.0%</t>
+          <t>-138.0%</t>
         </is>
       </c>
     </row>
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.22574762970317</v>
+        <v>-10.00519889602737</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9617838880017504</v>
+        <v>-0.8735643945314329</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.351660864180893</v>
+        <v>-2.1311121305051</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.717875069684728</v>
+        <v>1.850204309890204</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.44489659777736</v>
+        <v>-10.12193890205216</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.04640172460966</v>
+        <v>-0.9172186463195797</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.570809832255091</v>
+        <v>-2.24785213652989</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.589427439461978</v>
+        <v>1.783202056897099</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.44120567282095</v>
+        <v>-10.11824797709575</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.044925354627096</v>
+        <v>-0.9157422763370158</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.570809832255091</v>
+        <v>-2.24785213652989</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.589427439461978</v>
+        <v>1.783202056897099</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.64546384815082</v>
+        <v>-10.32250615242562</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.121115427640399</v>
+        <v>-0.9919323493503187</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.69844877686908</v>
+        <v>-2.375491081143879</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.518357269812227</v>
+        <v>1.712131887247348</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.86350161978199</v>
+        <v>-10.54054392405679</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.203847981808434</v>
+        <v>-1.074664903518354</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.873219544964979</v>
+        <v>-2.550261849239778</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.417977363439124</v>
+        <v>1.611751980874245</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.79003178811455</v>
+        <v>-10.46707409238934</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.159088347648034</v>
+        <v>-1.029905269357953</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.79974971329753</v>
+        <v>-2.476792017572329</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.477430963933014</v>
+        <v>1.671205581368135</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.96515620550109</v>
+        <v>-10.64219850977589</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.214582893855134</v>
+        <v>-1.085399815565053</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.974874130684074</v>
+        <v>-2.651916434958873</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.386911534248605</v>
+        <v>1.580686151683725</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.19960829951558</v>
+        <v>-10.87665060379038</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.315582896362526</v>
+        <v>-1.186399818072446</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.974874130684074</v>
+        <v>-2.651916434958873</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.379692369347009</v>
+        <v>1.573466986782129</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.48741214405282</v>
+        <v>-11.16445444832762</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.437376624951397</v>
+        <v>-1.308193546661317</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.262677975221312</v>
+        <v>-2.939720279496111</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.20033787185069</v>
+        <v>1.39411248928581</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.71723659121664</v>
+        <v>-11.39427889549144</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.528190613978371</v>
+        <v>-1.399007535688291</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.425325512291473</v>
+        <v>-3.102367816566272</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.10386513944715</v>
+        <v>1.29763975688227</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.9492655109529</v>
+        <v>-11.6263078152277</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.618308453243761</v>
+        <v>-1.489125374953681</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.487338209479896</v>
+        <v>-3.164380513754695</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.06935124976321</v>
+        <v>1.263125867198331</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.89724999698409</v>
+        <v>-11.57429230125889</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.593511911969835</v>
+        <v>-1.464328833679755</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.487338209479896</v>
+        <v>-3.164380513754695</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.073341585449611</v>
+        <v>1.267116202884732</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.03892183870821</v>
+        <v>-11.71596414298301</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.651655875558225</v>
+        <v>-1.522472797268144</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.487338209479896</v>
+        <v>-3.164380513754695</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.071866358550869</v>
+        <v>1.26564097598599</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.13782857916749</v>
+        <v>-11.81487088344229</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.676165161577063</v>
+        <v>-1.546982083286983</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.586244949939171</v>
+        <v>-3.26328725421397</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.027575724440177</v>
+        <v>1.221350341875297</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.93867647193039</v>
+        <v>-11.61571877620519</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.609555452328907</v>
+        <v>-1.480372374038826</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.420922423989358</v>
+        <v>-3.097964728264157</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.113718106363382</v>
+        <v>1.307492723798502</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.71283131921098</v>
+        <v>-11.38987362348578</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.509638318204934</v>
+        <v>-1.380455239914853</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.378995748402194</v>
+        <v>-3.056038052676993</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.148453184751888</v>
+        <v>1.342227802187009</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.42655650688828</v>
+        <v>-11.10359881116308</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.393989248719797</v>
+        <v>-1.264806170429716</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.378995748402194</v>
+        <v>-3.056038052676993</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.149592329307947</v>
+        <v>1.343366946743068</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.47945179493257</v>
+        <v>-11.15649409920737</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.412513589775403</v>
+        <v>-1.283330511485324</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.374040402313748</v>
+        <v>-3.051082706588547</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.155199311123123</v>
+        <v>1.348973928558243</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.19554306400382</v>
+        <v>-10.87258536827862</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.293216393165268</v>
+        <v>-1.164033314875187</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.374040402313748</v>
+        <v>-3.051082706588547</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.160933015361759</v>
+        <v>1.35470763279688</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.08012213986572</v>
+        <v>-10.75716444414052</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.256785285903894</v>
+        <v>-1.127602207613814</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.258619478175652</v>
+        <v>-2.935661782450452</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.220448307450752</v>
+        <v>1.414222924885872</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.81628527266165</v>
+        <v>-10.49332757693645</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.161134020335174</v>
+        <v>-1.031950942045094</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.258619478175652</v>
+        <v>-2.935661782450452</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.210564826137844</v>
+        <v>1.404339443572964</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.54904347179326</v>
+        <v>-10.22608577606806</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.056071860487189</v>
+        <v>-0.9268887821971084</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.258619478175652</v>
+        <v>-2.935661782450452</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.20873026563847</v>
+        <v>1.40250488307359</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.42573754331504</v>
+        <v>-10.10277984758984</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.007049804069362</v>
+        <v>-0.8778667257792816</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.169201807048089</v>
+        <v>-2.846244111322889</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.262080553341547</v>
+        <v>1.455855170776667</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.40178400233908</v>
+        <v>-10.07882630661388</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9967998815334851</v>
+        <v>-0.8676168032434046</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.145248266072132</v>
+        <v>-2.822290570346931</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.277121184072615</v>
+        <v>1.470895801507736</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.13772406401628</v>
+        <v>-9.814766368291082</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9044362223661189</v>
+        <v>-0.7752531440760384</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.881188327749336</v>
+        <v>-2.558230632024135</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.422296830904541</v>
+        <v>1.616071448339661</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.430644440511445</v>
+        <v>-9.107686744786244</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6243914066244844</v>
+        <v>-0.495208328334404</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.881188327749336</v>
+        <v>-2.558230632024135</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.41950979724424</v>
+        <v>1.61328441467936</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.390460142145255</v>
+        <v>-9.067502446420054</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6079740633901669</v>
+        <v>-0.4787909851000864</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.841004029383145</v>
+        <v>-2.518046333657944</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.443964000151796</v>
+        <v>1.637738617586916</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.216442860307177</v>
+        <v>-8.98743265088225</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5390003294341792</v>
+        <v>-0.447396245664208</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.666986747545067</v>
+        <v>-2.43797653812014</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.547741190475399</v>
+        <v>1.685147316130356</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.98296163807758</v>
+        <v>-8.753951428652652</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4376834117044877</v>
+        <v>-0.3460793279345165</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.433505525315469</v>
+        <v>-2.204495315890541</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.695754352651011</v>
+        <v>1.833160478305967</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.803253107933706</v>
+        <v>-8.574242898508778</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3686922099598973</v>
+        <v>-0.2770881261899261</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.376334021152772</v>
+        <v>-2.147323811727845</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.727165044835669</v>
+        <v>1.864571170490626</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.670977634302819</v>
+        <v>-8.441967424877891</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3204145337605153</v>
+        <v>-0.2288104499905441</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.244058547521886</v>
+        <v>-2.015048338096959</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.801897815761228</v>
+        <v>1.939303941416184</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.480377959629665</v>
+        <v>-8.251367750204738</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2413596032036174</v>
+        <v>-0.1497555194336462</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.053458872848733</v>
+        <v>-1.824448663423806</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.919072681252756</v>
+        <v>2.056478806907713</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.231378160946084</v>
+        <v>-8.002367951521157</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1288533425065261</v>
+        <v>-0.03724925873655494</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.053458872848733</v>
+        <v>-1.824448663423806</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.931979022476416</v>
+        <v>2.069385148131372</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.336968150719189</v>
+        <v>-8.107957941294261</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2990652680149868</v>
+        <v>-0.2074611842450156</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.159048862621838</v>
+        <v>-1.93003865319691</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.740649099013334</v>
+        <v>1.87805522466829</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.355703052837786</v>
+        <v>-8.126692843412858</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2580148869853391</v>
+        <v>-0.1664108032153679</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.159048862621838</v>
+        <v>-1.93003865319691</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.78919344089042</v>
+        <v>1.926599566545376</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.207763011430186</v>
+        <v>-7.978752802005259</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.318717793110467</v>
+        <v>-0.2271137093404958</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.13872794671328</v>
+        <v>-1.909717737288353</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.681507067747387</v>
+        <v>1.818913193402344</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.080870604995116</v>
+        <v>-7.851860395570188</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2766748167899169</v>
+        <v>-0.1850707330199457</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.01183554027821</v>
+        <v>-1.782825330853283</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.748928525354951</v>
+        <v>1.886334651009907</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.037322198224425</v>
+        <v>-7.808311988799498</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2662160661767334</v>
+        <v>-0.1746119824067627</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.01183554027821</v>
+        <v>-1.782825330853283</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.741967913259858</v>
+        <v>1.879374038914814</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.795173804770567</v>
+        <v>-7.56616359534564</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1548943544140471</v>
+        <v>-0.06329027064407633</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.01183554027821</v>
+        <v>-1.782825330853283</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.756430267641001</v>
+        <v>1.893836393295957</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.731944433002218</v>
+        <v>-7.502934223577292</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1350704852475131</v>
+        <v>-0.04346640147754233</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.01183554027821</v>
+        <v>-1.782825330853283</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.750962388100196</v>
+        <v>1.888368513755152</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.545456740625212</v>
+        <v>-7.316446531200286</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.06297731428613362</v>
+        <v>0.02862676948383713</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.825347847901204</v>
+        <v>-1.596337638476277</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.860353097536977</v>
+        <v>1.997759223191933</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.524307541721769</v>
+        <v>-7.295297332296842</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.04681665648743127</v>
+        <v>0.04478742728253948</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.804198648997761</v>
+        <v>-1.575188439572833</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.880743595116368</v>
+        <v>2.018149720771324</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.280542099738325</v>
+        <v>-7.051531890313398</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.04647022865299721</v>
+        <v>0.138074312422968</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.804198648997761</v>
+        <v>-1.575188439572833</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.876524303463418</v>
+        <v>2.013930429118375</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.016514032545064</v>
+        <v>-6.787503823120138</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1542057694503174</v>
+        <v>0.2458098532202877</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.602333250181807</v>
+        <v>-1.37332304075688</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.999767856673007</v>
+        <v>2.137173982327963</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.76666363859599</v>
+        <v>-6.537653429171064</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2468880020136495</v>
+        <v>0.3384920857836198</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.602333250181807</v>
+        <v>-1.37332304075688</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.992509931656709</v>
+        <v>2.129916057311665</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.463096149592011</v>
+        <v>-6.234085940167085</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3719141211358896</v>
+        <v>0.4635182049058599</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.602333250181807</v>
+        <v>-1.37332304075688</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.996109055177357</v>
+        <v>2.133515180832314</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.389616240739997</v>
+        <v>-6.160606031315071</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4146335907312491</v>
+        <v>0.5062376745012194</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.528853341329793</v>
+        <v>-1.299843131904865</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.05352450654312</v>
+        <v>2.190930632198076</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.164583241071174</v>
+        <v>-5.935573031646248</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5036672682150751</v>
+        <v>0.5952713519850454</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.30382034166097</v>
+        <v>-1.074810132236042</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.187564783960711</v>
+        <v>2.324970909615667</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.949948863434767</v>
+        <v>-5.720938654009841</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5942158203239551</v>
+        <v>0.6858199040939255</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.089185964024563</v>
+        <v>-0.8601757545996356</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.321040211596872</v>
+        <v>2.458446337251829</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.683348506460415</v>
+        <v>-5.454338297035489</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6820502218974918</v>
+        <v>0.7736543056674621</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.089185964024563</v>
+        <v>-0.8601757545996356</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.302234470380668</v>
+        <v>2.439640596035624</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.442918009655555</v>
+        <v>-5.213907800230629</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7799654972443131</v>
+        <v>0.8715695810142834</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8487554672197026</v>
+        <v>-0.6197452577947753</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.448235845088461</v>
+        <v>2.585641970743418</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.20012720200611</v>
+        <v>-4.971116992581184</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8810111341389115</v>
+        <v>0.9726152179088818</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8487554672197026</v>
+        <v>-0.6197452577947753</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.452165158923282</v>
+        <v>2.589571284578238</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.084187352380924</v>
+        <v>-4.855177142955998</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9280656579063256</v>
+        <v>1.019669741676296</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7719337362035787</v>
+        <v>-0.5429235267786514</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.498936781450296</v>
+        <v>2.636342907105252</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.841531763957761</v>
+        <v>-4.612521554532835</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.022125964495584</v>
+        <v>1.113730048265555</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7719337362035787</v>
+        <v>-0.5429235267786514</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.495934852670289</v>
+        <v>2.633340978325246</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.62151096592075</v>
+        <v>-4.392500756495824</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.111713320721003</v>
+        <v>1.203317404490973</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6307138911355985</v>
+        <v>-0.4017036817106712</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.582245796721692</v>
+        <v>2.719651922376648</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.521051165760024</v>
+        <v>-4.193252126591015</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.167791423587117</v>
+        <v>1.29891103925472</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6307138911355985</v>
+        <v>-0.4017036817106712</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.598139979523514</v>
+        <v>2.735546105178471</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.361536062240654</v>
+        <v>-4.033737023071645</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.232743309435166</v>
+        <v>1.36386292510277</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4711987876162286</v>
+        <v>-0.2421885781913012</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.694994886075439</v>
+        <v>2.832401011730395</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.216863917140917</v>
+        <v>-3.889064877971908</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.300700270036501</v>
+        <v>1.431819885704105</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3265266425164912</v>
+        <v>-0.09751643309156383</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.791886275696721</v>
+        <v>2.929292401351677</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.199094458209961</v>
+        <v>-3.871295419040953</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.223147745695605</v>
+        <v>1.354267361363209</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3087571835855356</v>
+        <v>-0.07974697416060827</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.717887643142016</v>
+        <v>2.855293768796972</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.112294960430953</v>
+        <v>-3.784495921261944</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.280268038129775</v>
+        <v>1.411387653797378</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3087571835855356</v>
+        <v>-0.07974697416060827</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.740288136464582</v>
+        <v>2.877694262119538</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.012602345701941</v>
+        <v>-3.684803306532932</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.320217485394791</v>
+        <v>1.451337101062395</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2090645688565239</v>
+        <v>0.01994564056840348</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.800176106675401</v>
+        <v>2.937582232330358</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.080972532025951</v>
+        <v>-3.753173492856942</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.303876333339889</v>
+        <v>1.434995949007493</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1997888698203089</v>
+        <v>0.02922133960461842</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.816748448571832</v>
+        <v>2.954154574226788</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.959556102399475</v>
+        <v>-3.631757063230465</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.342879613822371</v>
+        <v>1.473999229489975</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1997888698203089</v>
+        <v>0.02922133960461842</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.807185157203723</v>
+        <v>2.94459128285868</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.99054926172818</v>
+        <v>-3.662750222559171</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.155191915131276</v>
+        <v>1.28631153079888</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1997888698203089</v>
+        <v>0.02922133960461842</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.63189472224411</v>
+        <v>2.769300847899066</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.815075001935711</v>
+        <v>-3.487275962766701</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.229948851040051</v>
+        <v>1.361068466707655</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1997888698203089</v>
+        <v>0.02922133960461842</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.636461954235898</v>
+        <v>2.773868079890854</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.926011254576959</v>
+        <v>-3.59821221540795</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.18558582387035</v>
+        <v>1.316705439537953</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1997888698203089</v>
+        <v>0.02922133960461842</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.636473428122696</v>
+        <v>2.773879553777652</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.129037832120193</v>
+        <v>-3.801238792951183</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.107506578072962</v>
+        <v>1.238626193740565</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4028154473635423</v>
+        <v>-0.173805237938615</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.517788866816661</v>
+        <v>2.655194992471618</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.561523597899424</v>
+        <v>3.848204107564892</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.636724498191444</v>
+        <v>3.087553972360432</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.129037832120193</v>
+        <v>-3.801238792951183</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.107506578072962</v>
+        <v>1.238626193740565</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4028154473635423</v>
+        <v>-0.173805237938615</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.629788295177812</v>
+        <v>3.0806177693468</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240422.xlsx
+++ b/tame_output/ON/bt/strategyON_20240422.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,35 +811,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-37.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>115.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.1%</t>
+          <t>135.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-669.8%</t>
+          <t>-671.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.4%</t>
+          <t>-56.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.8%</t>
+          <t>783.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-541.7%</t>
+          <t>-570.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.3%</t>
+          <t>-43.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-45.9%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-252.4%</t>
+          <t>-263.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-36.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.7%</t>
+          <t>-160.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-241.4%</t>
+          <t>-270.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.0%</t>
+          <t>-172.8%</t>
         </is>
       </c>
     </row>
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.00519889602737</v>
+        <v>-10.22574762970317</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8735643945314329</v>
+        <v>-0.9617838880017504</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.1311121305051</v>
+        <v>-2.351660864180893</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.850204309890204</v>
+        <v>1.717875069684728</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.12193890205216</v>
+        <v>-10.30729204436703</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9172186463195797</v>
+        <v>-0.9913599032455269</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.24785213652989</v>
+        <v>-2.433205278844757</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.783202056897099</v>
+        <v>1.671990171508179</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.11824797709575</v>
+        <v>-10.30360111941062</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9157422763370158</v>
+        <v>-0.9898835332629621</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.24785213652989</v>
+        <v>-2.433205278844757</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.783202056897099</v>
+        <v>1.671990171508179</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.32250615242562</v>
+        <v>-10.50785929474048</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9919323493503187</v>
+        <v>-1.066073606276266</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.375491081143879</v>
+        <v>-2.560844223458746</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.712131887247348</v>
+        <v>1.600920001858428</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.54054392405679</v>
+        <v>-10.72589706637166</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.074664903518354</v>
+        <v>-1.148806160444301</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.550261849239778</v>
+        <v>-2.735614991554645</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.611751980874245</v>
+        <v>1.500540095485324</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.46707409238934</v>
+        <v>-10.65242723470421</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.029905269357953</v>
+        <v>-1.104046526283899</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.476792017572329</v>
+        <v>-2.662145159887196</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.671205581368135</v>
+        <v>1.559993695979215</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.64219850977589</v>
+        <v>-10.82755165209075</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.085399815565053</v>
+        <v>-1.159541072491001</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.651916434958873</v>
+        <v>-2.83726957727374</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.580686151683725</v>
+        <v>1.469474266294805</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.87665060379038</v>
+        <v>-11.06200374610524</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.186399818072446</v>
+        <v>-1.260541074998392</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.651916434958873</v>
+        <v>-2.83726957727374</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.573466986782129</v>
+        <v>1.462255101393209</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.16445444832762</v>
+        <v>-11.34980759064248</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.308193546661317</v>
+        <v>-1.382334803587264</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.939720279496111</v>
+        <v>-3.125073421810978</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.39411248928581</v>
+        <v>1.28290060389689</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.39427889549144</v>
+        <v>-11.57963203780631</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.399007535688291</v>
+        <v>-1.473148792614237</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.102367816566272</v>
+        <v>-3.287720958881139</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.29763975688227</v>
+        <v>1.18642787149335</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.6263078152277</v>
+        <v>-11.81166095754257</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.489125374953681</v>
+        <v>-1.563266631879628</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.164380513754695</v>
+        <v>-3.349733656069562</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.263125867198331</v>
+        <v>1.151913981809411</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.57429230125889</v>
+        <v>-11.75964544357376</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.464328833679755</v>
+        <v>-1.538470090605702</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.164380513754695</v>
+        <v>-3.349733656069562</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.267116202884732</v>
+        <v>1.155904317495811</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.71596414298301</v>
+        <v>-11.90131728529788</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.522472797268144</v>
+        <v>-1.596614054194092</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.164380513754695</v>
+        <v>-3.349733656069562</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.26564097598599</v>
+        <v>1.15442909059707</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.81487088344229</v>
+        <v>-12.00022402575715</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.546982083286983</v>
+        <v>-1.621123340212929</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.26328725421397</v>
+        <v>-3.448640396528837</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.221350341875297</v>
+        <v>1.110138456486377</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.61571877620519</v>
+        <v>-11.80107191852005</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.480372374038826</v>
+        <v>-1.554513630964772</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.097964728264157</v>
+        <v>-3.283317870579024</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.307492723798502</v>
+        <v>1.196280838409582</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.38987362348578</v>
+        <v>-11.57522676580064</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.380455239914853</v>
+        <v>-1.4545964968408</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.056038052676993</v>
+        <v>-3.24139119499186</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.342227802187009</v>
+        <v>1.231015916798089</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.10359881116308</v>
+        <v>-11.28895195347795</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.264806170429716</v>
+        <v>-1.338947427355663</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.056038052676993</v>
+        <v>-3.24139119499186</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.343366946743068</v>
+        <v>1.232155061354148</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.15649409920737</v>
+        <v>-11.34184724152223</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.283330511485324</v>
+        <v>-1.35747176841127</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.051082706588547</v>
+        <v>-3.236435848903414</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.348973928558243</v>
+        <v>1.237762043169323</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.87258536827862</v>
+        <v>-11.05793851059349</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.164033314875187</v>
+        <v>-1.238174571801134</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.051082706588547</v>
+        <v>-3.236435848903414</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.35470763279688</v>
+        <v>1.24349574740796</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.75716444414052</v>
+        <v>-10.94251758645539</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.127602207613814</v>
+        <v>-1.201743464539761</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.935661782450452</v>
+        <v>-3.121014924765318</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.414222924885872</v>
+        <v>1.303011039496952</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.49332757693645</v>
+        <v>-10.67868071925132</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.031950942045094</v>
+        <v>-1.10609219897104</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.935661782450452</v>
+        <v>-3.121014924765318</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.404339443572964</v>
+        <v>1.293127558184044</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.22608577606806</v>
+        <v>-10.41143891838292</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9268887821971084</v>
+        <v>-1.001030039123055</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.935661782450452</v>
+        <v>-3.121014924765318</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.40250488307359</v>
+        <v>1.291292997684671</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.10277984758984</v>
+        <v>-10.2881329899047</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8778667257792816</v>
+        <v>-0.9520079827052279</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.846244111322889</v>
+        <v>-3.031597253637755</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.455855170776667</v>
+        <v>1.344643285387747</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.07882630661388</v>
+        <v>-10.26417944892875</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8676168032434046</v>
+        <v>-0.9417580601693518</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.822290570346931</v>
+        <v>-3.007643712661798</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.470895801507736</v>
+        <v>1.359683916118816</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.814766368291082</v>
+        <v>-10.00011951060595</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7752531440760384</v>
+        <v>-0.8493944010019847</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.558230632024135</v>
+        <v>-2.743583774339001</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.616071448339661</v>
+        <v>1.504859562950741</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.107686744786244</v>
+        <v>-9.293039887101111</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.495208328334404</v>
+        <v>-0.5693495852603507</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.558230632024135</v>
+        <v>-2.743583774339001</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.61328441467936</v>
+        <v>1.50207252929044</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.067502446420054</v>
+        <v>-9.252855588734921</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4787909851000864</v>
+        <v>-0.5529322420260332</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.518046333657944</v>
+        <v>-2.703399475972811</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.637738617586916</v>
+        <v>1.526526732197996</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.98743265088225</v>
+        <v>-9.172785793197116</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.447396245664208</v>
+        <v>-0.5215375025901547</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.43797653812014</v>
+        <v>-2.623329680435007</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.685147316130356</v>
+        <v>1.573935430741436</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.753951428652652</v>
+        <v>-8.939304570967519</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3460793279345165</v>
+        <v>-0.4202205848604632</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.204495315890541</v>
+        <v>-2.389848458205408</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.833160478305967</v>
+        <v>1.721948592917047</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.574242898508778</v>
+        <v>-8.759596040823645</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2770881261899261</v>
+        <v>-0.3512293831158728</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.147323811727845</v>
+        <v>-2.332676954042712</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.864571170490626</v>
+        <v>1.753359285101705</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.441967424877891</v>
+        <v>-8.627320567192758</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2288104499905441</v>
+        <v>-0.3029517069164909</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.015048338096959</v>
+        <v>-2.200401480411826</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.939303941416184</v>
+        <v>1.828092056027264</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.251367750204738</v>
+        <v>-8.436720892519604</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1497555194336462</v>
+        <v>-0.2238967763595929</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.824448663423806</v>
+        <v>-2.009801805738673</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.056478806907713</v>
+        <v>1.945266921518793</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.002367951521157</v>
+        <v>-8.187721093836023</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.03724925873655494</v>
+        <v>-0.1113905156625017</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.824448663423806</v>
+        <v>-2.009801805738673</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.069385148131372</v>
+        <v>1.958173262742451</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.107957941294261</v>
+        <v>-8.293311083609128</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2074611842450156</v>
+        <v>-0.2816024411709623</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.93003865319691</v>
+        <v>-2.115391795511777</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.87805522466829</v>
+        <v>1.76684333927937</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.126692843412858</v>
+        <v>-8.312045985727725</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1664108032153679</v>
+        <v>-0.2405520601413147</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.93003865319691</v>
+        <v>-2.115391795511777</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.926599566545376</v>
+        <v>1.815387681156457</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.978752802005259</v>
+        <v>-8.164105944320125</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2271137093404958</v>
+        <v>-0.3012549662664425</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.909717737288353</v>
+        <v>-2.09507087960322</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.818913193402344</v>
+        <v>1.707701308013424</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.851860395570188</v>
+        <v>-8.037213537885055</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1850707330199457</v>
+        <v>-0.2592119899458925</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.782825330853283</v>
+        <v>-1.96817847316815</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.886334651009907</v>
+        <v>1.775122765620987</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.808311988799498</v>
+        <v>-7.993665131114365</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1746119824067627</v>
+        <v>-0.2487532393327094</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.782825330853283</v>
+        <v>-1.96817847316815</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.879374038914814</v>
+        <v>1.768162153525894</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.56616359534564</v>
+        <v>-7.751516737660507</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.06329027064407633</v>
+        <v>-0.1374315275700231</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.782825330853283</v>
+        <v>-1.96817847316815</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.893836393295957</v>
+        <v>1.782624507907037</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.502934223577292</v>
+        <v>-7.688287365892158</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.04346640147754233</v>
+        <v>-0.1176076584034886</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.782825330853283</v>
+        <v>-1.96817847316815</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.888368513755152</v>
+        <v>1.777156628366232</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.316446531200286</v>
+        <v>-7.501799673515152</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.02862676948383713</v>
+        <v>-0.04551448744210962</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.596337638476277</v>
+        <v>-1.781690780791144</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.997759223191933</v>
+        <v>1.886547337803013</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.295297332296842</v>
+        <v>-7.480650474611709</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.04478742728253948</v>
+        <v>-0.02935382964340683</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.575188439572833</v>
+        <v>-1.7605415818877</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.018149720771324</v>
+        <v>1.906937835382404</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.051531890313398</v>
+        <v>-7.236885032628265</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.138074312422968</v>
+        <v>0.06393305549702122</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.575188439572833</v>
+        <v>-1.7605415818877</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.013930429118375</v>
+        <v>1.902718543729455</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.787503823120138</v>
+        <v>-6.972856965435005</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2458098532202877</v>
+        <v>0.1716685962943414</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.37332304075688</v>
+        <v>-1.558676183071747</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.137173982327963</v>
+        <v>2.025962096939043</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.537653429171064</v>
+        <v>-6.72300657148593</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3384920857836198</v>
+        <v>0.264350828857673</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.37332304075688</v>
+        <v>-1.558676183071747</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.129916057311665</v>
+        <v>2.018704171922745</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.234085940167085</v>
+        <v>-6.419439082481952</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4635182049058599</v>
+        <v>0.3893769479799136</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.37332304075688</v>
+        <v>-1.558676183071747</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.133515180832314</v>
+        <v>2.022303295443394</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.160606031315071</v>
+        <v>-6.345959173629938</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5062376745012194</v>
+        <v>0.4320964175752726</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.299843131904865</v>
+        <v>-1.485196274219732</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.190930632198076</v>
+        <v>2.079718746809156</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.935573031646248</v>
+        <v>-6.120926173961115</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5952713519850454</v>
+        <v>0.5211300950590987</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.074810132236042</v>
+        <v>-1.260163274550909</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.324970909615667</v>
+        <v>2.213759024226747</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.720938654009841</v>
+        <v>-5.906291796324708</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6858199040939255</v>
+        <v>0.6116786471679792</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8601757545996356</v>
+        <v>-1.045528896914503</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.458446337251829</v>
+        <v>2.347234451862908</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.454338297035489</v>
+        <v>-5.639691439350356</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7736543056674621</v>
+        <v>0.6995130487415153</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8601757545996356</v>
+        <v>-1.045528896914503</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.439640596035624</v>
+        <v>2.328428710646704</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.213907800230629</v>
+        <v>-5.399260942545496</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8715695810142834</v>
+        <v>0.7974283240883366</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6197452577947753</v>
+        <v>-0.8050984001096424</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.585641970743418</v>
+        <v>2.474430085354497</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.971116992581184</v>
+        <v>-5.15647013489605</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9726152179088818</v>
+        <v>0.8984739609829351</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6197452577947753</v>
+        <v>-0.8050984001096424</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.589571284578238</v>
+        <v>2.478359399189317</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.855177142955998</v>
+        <v>-5.040530285270865</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.019669741676296</v>
+        <v>0.9455284847503491</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5429235267786514</v>
+        <v>-0.7282766690935185</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.636342907105252</v>
+        <v>2.525131021716332</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.612521554532835</v>
+        <v>-4.797874696847702</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.113730048265555</v>
+        <v>1.039588791339608</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5429235267786514</v>
+        <v>-0.7282766690935185</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.633340978325246</v>
+        <v>2.522129092936325</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.392500756495824</v>
+        <v>-4.577853898810691</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.203317404490973</v>
+        <v>1.129176147565027</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4017036817106712</v>
+        <v>-0.5870568240255383</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.719651922376648</v>
+        <v>2.608440036987727</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.193252126591015</v>
+        <v>-4.378605268905882</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.29891103925472</v>
+        <v>1.224769782328774</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4017036817106712</v>
+        <v>-0.5870568240255383</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.735546105178471</v>
+        <v>2.624334219789551</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.033737023071645</v>
+        <v>-4.32037636426459</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.36386292510277</v>
+        <v>1.249207188625592</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2421885781913012</v>
+        <v>-0.5288279193842461</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.832401011730395</v>
+        <v>2.660417407014628</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.889064877971908</v>
+        <v>-4.175704219164852</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.431819885704105</v>
+        <v>1.317164149226927</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09751643309156383</v>
+        <v>-0.3841557742845087</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.929292401351677</v>
+        <v>2.75730879663591</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.871295419040953</v>
+        <v>-4.157934760233896</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.354267361363209</v>
+        <v>1.239611624886031</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.07974697416060827</v>
+        <v>-0.3663863153535531</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.855293768796972</v>
+        <v>2.683310164081205</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.784495921261944</v>
+        <v>-4.071135262454888</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.411387653797378</v>
+        <v>1.296731917320201</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.07974697416060827</v>
+        <v>-0.3663863153535531</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.877694262119538</v>
+        <v>2.705710657403771</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.684803306532932</v>
+        <v>-3.971442647725876</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.451337101062395</v>
+        <v>1.336681364585217</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.01994564056840348</v>
+        <v>-0.2666937006245414</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.937582232330358</v>
+        <v>2.765598627614591</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.753173492856942</v>
+        <v>-4.039812834049886</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.434995949007493</v>
+        <v>1.320340212530315</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02922133960461842</v>
+        <v>-0.2574180015883265</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.954154574226788</v>
+        <v>2.782170969511021</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.631757063230465</v>
+        <v>-3.91839640442341</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.473999229489975</v>
+        <v>1.359343493012797</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02922133960461842</v>
+        <v>-0.2574180015883265</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.94459128285868</v>
+        <v>2.772607678142913</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.662750222559171</v>
+        <v>-3.949389563752115</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.28631153079888</v>
+        <v>1.171655794321702</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02922133960461842</v>
+        <v>-0.2574180015883265</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.769300847899066</v>
+        <v>2.5973172431833</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.487275962766701</v>
+        <v>-3.773915303959646</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.361068466707655</v>
+        <v>1.246412730230477</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02922133960461842</v>
+        <v>-0.2574180015883265</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.773868079890854</v>
+        <v>2.601884475175087</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.59821221540795</v>
+        <v>-3.884851556600895</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.316705439537953</v>
+        <v>1.202049703060776</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02922133960461842</v>
+        <v>-0.2574180015883265</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.773879553777652</v>
+        <v>2.601895949061885</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.801238792951183</v>
+        <v>-4.087878134144128</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.238626193740565</v>
+        <v>1.123970457263388</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.173805237938615</v>
+        <v>-0.4604445791315598</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.655194992471618</v>
+        <v>2.48321138775585</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.848204107564892</v>
+        <v>3.566529876865731</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.087553972360432</v>
+        <v>2.739074085594588</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.801238792951183</v>
+        <v>-4.087878134144128</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.238626193740565</v>
+        <v>1.123970457263388</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.173805237938615</v>
+        <v>-0.4604445791315598</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.0806177693468</v>
+        <v>2.732137882580956</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240422.xlsx
+++ b/tame_output/ON/bt/strategyON_20240422.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>58.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-35.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.7%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.4%</t>
+          <t>135.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-671.9%</t>
+          <t>-696.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-56.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>783.8%</t>
+          <t>548.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.4%</t>
+          <t>-584.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.3%</t>
+          <t>-272.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.8%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-263.8%</t>
+          <t>-269.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.7%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.1%</t>
+          <t>-159.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-270.0%</t>
+          <t>-283.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-172.8%</t>
+          <t>-170.7%</t>
         </is>
       </c>
     </row>
@@ -43641,10 +43641,10 @@
         <v>3.127238527942291</v>
       </c>
       <c r="D1830" t="n">
-        <v>1.26606255345954</v>
+        <v>1.400718067685997</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.633307125012359</v>
+        <v>3.687169330702942</v>
       </c>
       <c r="F1830" t="n">
         <v>2.239927473767815</v>
@@ -43664,10 +43664,10 @@
         <v>3.12760327346781</v>
       </c>
       <c r="D1831" t="n">
-        <v>1.24701080845007</v>
+        <v>1.381666322676527</v>
       </c>
       <c r="E1831" t="n">
-        <v>3.62605117253409</v>
+        <v>3.679913378224673</v>
       </c>
       <c r="F1831" t="n">
         <v>2.220875728758345</v>
@@ -43687,10 +43687,10 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.242410788905723</v>
+        <v>1.37706630313218</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.62667717033905</v>
+        <v>3.680539376029633</v>
       </c>
       <c r="F1832" t="n">
         <v>2.216275709213999</v>
@@ -43710,10 +43710,10 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.194572426659524</v>
+        <v>1.329227940885981</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.604413879342283</v>
+        <v>3.658276085032866</v>
       </c>
       <c r="F1833" t="n">
         <v>2.216275709213999</v>
@@ -43733,10 +43733,10 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.858629459151194</v>
+        <v>0.9932849733776514</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.483013301622341</v>
+        <v>3.536875507312923</v>
       </c>
       <c r="F1834" t="n">
         <v>1.880332741705669</v>
@@ -43756,10 +43756,10 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.9927331735358391</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.534912623238543</v>
       </c>
       <c r="F1835" t="n">
         <v>1.881174505190975</v>
@@ -43779,10 +43779,10 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.8870462855935395</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.47246314068907</v>
       </c>
       <c r="F1836" t="n">
         <v>1.866613431488292</v>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.5703842080441135</v>
+        <v>0.7050397222705709</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.346287448395174</v>
+        <v>3.400149654085757</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.52216194119703</v>
+        <v>0.6568174554234874</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.331078524278007</v>
+        <v>3.38494072996859</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2850304493472349</v>
+        <v>0.4196859635736923</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.271167012035631</v>
+        <v>3.325029217726214</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2900680400748214</v>
+        <v>0.4247235543012788</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.271759488512004</v>
+        <v>3.325621694202586</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1274419601101828</v>
+        <v>0.2620974743366402</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.185455438149885</v>
+        <v>3.239317643840468</v>
       </c>
       <c r="F1841" t="n">
         <v>1.711409540942887</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.06167457006077076</v>
+        <v>0.1963300842872281</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.160166091260591</v>
+        <v>3.214028296951174</v>
       </c>
       <c r="F1842" t="n">
         <v>1.711409540942887</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.04813908628406116</v>
+        <v>0.1827946005105185</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.145379929737663</v>
+        <v>3.199242135428245</v>
       </c>
       <c r="F1843" t="n">
         <v>1.711409540942887</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.03363281414369051</v>
+        <v>0.1010227000827669</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.1027538955218</v>
+        <v>3.156616101212383</v>
       </c>
       <c r="F1844" t="n">
         <v>1.738445114349024</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.1008419220155682</v>
+        <v>0.0338135922108892</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.080635569206751</v>
+        <v>3.134497774897334</v>
       </c>
       <c r="F1845" t="n">
         <v>1.738445114349024</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.3084077064071801</v>
+        <v>-0.1737521921807227</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.995434051569347</v>
+        <v>3.04929625725993</v>
       </c>
       <c r="F1846" t="n">
         <v>1.530879329957412</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7261617299540171</v>
+        <v>-0.5915062157275597</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.826259333655675</v>
+        <v>2.880121539346258</v>
       </c>
       <c r="F1847" t="n">
         <v>1.113125306410575</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9477836635121346</v>
+        <v>-0.8131281492856772</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.73747677683135</v>
+        <v>2.791338982521933</v>
       </c>
       <c r="F1848" t="n">
         <v>1.075599172723206</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.155787721865212</v>
+        <v>-1.021132207638755</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.659167298044044</v>
+        <v>2.713029503734627</v>
       </c>
       <c r="F1849" t="n">
         <v>1.075599172723206</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.367200142753187</v>
+        <v>-1.23254462852673</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.569683786026842</v>
+        <v>2.623545991717426</v>
       </c>
       <c r="F1850" t="n">
         <v>0.8641867518352306</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.706358520341709</v>
+        <v>-1.571703006115252</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.427104734297883</v>
+        <v>2.480966939988466</v>
       </c>
       <c r="F1851" t="n">
         <v>0.5250283742467086</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.034375742069188</v>
+        <v>-1.899720227842731</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.316236135345659</v>
+        <v>2.370098341036242</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1970111525192294</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.527700613604366</v>
+        <v>-2.393045099377909</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.127004937140156</v>
+        <v>2.180867142830739</v>
       </c>
       <c r="F1853" t="n">
         <v>0.09202503827961067</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.020085641628463</v>
+        <v>-2.885430127402006</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.93115731797425</v>
+        <v>1.985019523664833</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4003599897444861</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.405266032558536</v>
+        <v>-3.270610518332079</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.775627700415084</v>
+        <v>1.829489906105667</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4003599897444861</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.748948805785199</v>
+        <v>-3.614293291558742</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.639923714579035</v>
+        <v>1.693785920269618</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5082660417717042</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.106599156023547</v>
+        <v>-3.97194364179709</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.492969633139954</v>
+        <v>1.546831838830537</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.8659163920100523</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.415833259019598</v>
+        <v>-4.281177744793141</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.371048918641793</v>
+        <v>1.424911124332376</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.8659163920100523</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.847639052169385</v>
+        <v>-4.712983537942928</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.184659488849283</v>
+        <v>1.238521694539865</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.002333888451319</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.082333046301938</v>
+        <v>-4.94767753207548</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.079066666198352</v>
+        <v>1.132928871888935</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.9959976212220641</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.41799569353239</v>
+        <v>-5.283340179305933</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9433821989621363</v>
+        <v>0.9972444046527191</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.9959976212220641</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.781621938432703</v>
+        <v>-5.646966424206246</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8044192612362524</v>
+        <v>0.8582814669268357</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.09421925808919</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.14674932107145</v>
+        <v>-6.012093806844993</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.657622823186585</v>
+        <v>0.7114850288771684</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.390530042388202</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.555338098252129</v>
+        <v>-6.420682584025672</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4929488563290727</v>
+        <v>0.5468110620196556</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.799118819568881</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.968320582393223</v>
+        <v>-6.833665068166765</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.322941295144096</v>
+        <v>0.3768035008346788</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.799118819568881</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.38471245668022</v>
+        <v>-7.250056942453763</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1543785960381743</v>
+        <v>0.2082408017287571</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.799118819568881</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.761389467210065</v>
+        <v>-7.626733952983607</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0139664824949155</v>
+        <v>0.06782868818549836</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.799118819568881</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.107264289194873</v>
+        <v>-7.972608774968416</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1282838811533127</v>
+        <v>-0.07442167546272982</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.799118819568881</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.269406559657966</v>
+        <v>-8.134751045431509</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1947358692835492</v>
+        <v>-0.1408736635929659</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.799118819568881</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.566067901468164</v>
+        <v>-8.431412387241707</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3096214300784204</v>
+        <v>-0.255759224387837</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.867861955302759</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.9994170095784</v>
+        <v>-8.864761495351942</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4869873778569174</v>
+        <v>-0.4331251721663345</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.867861955302759</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.382418398321031</v>
+        <v>-9.247762884094573</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6402900346755538</v>
+        <v>-0.5864278289849709</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.867861955302759</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.539817278534152</v>
+        <v>-9.405161764307694</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7006780707893721</v>
+        <v>-0.6468158650987892</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.02526083551588</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.899347601038153</v>
+        <v>-9.764692086811696</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8391398964929224</v>
+        <v>-0.7852776908023396</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.02526083551588</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.22574762970317</v>
+        <v>-10.09109211547671</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9617838880017504</v>
+        <v>-0.9079216823111671</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.351660864180893</v>
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.30729204436703</v>
+        <v>-10.31024108355091</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9913599032455269</v>
+        <v>-0.9925395189190778</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.433205278844757</v>
+        <v>-2.570809832255091</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.671990171508179</v>
+        <v>1.589427439461978</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.131913338815032</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.30360111941062</v>
+        <v>-10.41235234558823</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9898835332629621</v>
+        <v>-1.030490467412433</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.433205278844757</v>
+        <v>-2.672921094292411</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.671990171508179</v>
+        <v>1.531054238561158</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.137426535933675</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.50785929474048</v>
+        <v>-10.61661052091809</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.066073606276266</v>
+        <v>-1.106680540425737</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.560844223458746</v>
+        <v>-2.8005600389064</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.600920001858428</v>
+        <v>1.459984068911407</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.141909090418111</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.72589706637166</v>
+        <v>-10.83464829254927</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.148806160444301</v>
+        <v>-1.189413094593772</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.735614991554645</v>
+        <v>-2.975330807002299</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.500540095485324</v>
+        <v>1.359604162538304</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.157280791911532</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.65242723470421</v>
+        <v>-10.76117846088182</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.104046526283899</v>
+        <v>-1.14465346043337</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.662145159887196</v>
+        <v>-2.901860975334851</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.559993695979215</v>
+        <v>1.419057763032194</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.171836012659049</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.82755165209075</v>
+        <v>-10.93630287826836</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.159541072491001</v>
+        <v>-1.200148006640472</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.83726957727374</v>
+        <v>-3.076985392721395</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.469474266294805</v>
+        <v>1.328538333347784</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.164616847757453</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.06200374610524</v>
+        <v>-11.17075497228285</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.260541074998392</v>
+        <v>-1.301148009147863</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.83726957727374</v>
+        <v>-3.076985392721395</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.462255101393209</v>
+        <v>1.321319168446188</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.157944656983477</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.34980759064248</v>
+        <v>-11.45855881682009</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.382334803587264</v>
+        <v>-1.422941737736735</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.125073421810978</v>
+        <v>-3.364789237258633</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.28290060389689</v>
+        <v>1.14196467094987</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.159060446822033</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.57963203780631</v>
+        <v>-11.68838326398392</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.473148792614237</v>
+        <v>-1.513755726763709</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.287720958881139</v>
+        <v>-3.527436774328793</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.18642787149335</v>
+        <v>1.045491938546329</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.161754175451148</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.81166095754257</v>
+        <v>-11.92041218372018</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.563266631879628</v>
+        <v>-1.603873566029099</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.349733656069562</v>
+        <v>-3.589449471517216</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.151913981809411</v>
+        <v>1.01097804886239</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.165744511137548</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.75964544357376</v>
+        <v>-11.86839666975136</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.538470090605702</v>
+        <v>-1.579077024755173</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.349733656069562</v>
+        <v>-3.589449471517216</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.155904317495811</v>
+        <v>1.014968384548791</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.164269284238807</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.90131728529788</v>
+        <v>-12.01006851147548</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.596614054194092</v>
+        <v>-1.637220988343563</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.349733656069562</v>
+        <v>-3.589449471517216</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.15442909059707</v>
+        <v>1.013493157650049</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.179322694403679</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.00022402575715</v>
+        <v>-12.10897525193476</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.621123340212929</v>
+        <v>-1.6617302743624</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.448640396528837</v>
+        <v>-3.688356211976492</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.110138456486377</v>
+        <v>0.9692025235393564</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.166271560756996</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.80107191852005</v>
+        <v>-11.90982314469766</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.554513630964772</v>
+        <v>-1.595120565114243</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.283317870579024</v>
+        <v>-3.523033686026678</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.196280838409582</v>
+        <v>1.055344905462562</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.175850633793205</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.57522676580064</v>
+        <v>-11.68397799197825</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.4545964968408</v>
+        <v>-1.495203430990271</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.24139119499186</v>
+        <v>-3.481107010439515</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.231015916798089</v>
+        <v>1.090079983851068</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.176989778349264</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.28895195347795</v>
+        <v>-11.39770317965555</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.338947427355663</v>
+        <v>-1.379554361505134</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.24139119499186</v>
+        <v>-3.481107010439515</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.232155061354148</v>
+        <v>1.091219128407127</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.179623552511371</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.34184724152223</v>
+        <v>-11.45059846769984</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.35747176841127</v>
+        <v>-1.39807870256074</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.236435848903414</v>
+        <v>-3.476151664351069</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.237762043169323</v>
+        <v>1.096826110222302</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.185357256750008</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.05793851059349</v>
+        <v>-11.16668973677109</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.238174571801134</v>
+        <v>-1.278781505950604</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.236435848903414</v>
+        <v>-3.476151664351069</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.24349574740796</v>
+        <v>1.102559814460939</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.175619994356143</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.94251758645539</v>
+        <v>-11.051268812633</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.201743464539761</v>
+        <v>-1.242350398689231</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.121014924765318</v>
+        <v>-3.360730740212973</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.303011039496952</v>
+        <v>1.162075106549931</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.165736513043235</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.67868071925132</v>
+        <v>-10.78743194542893</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.10609219897104</v>
+        <v>-1.146699133120511</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.121014924765318</v>
+        <v>-3.360730740212973</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.293127558184044</v>
+        <v>1.152191625237024</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.163901952543861</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.41143891838292</v>
+        <v>-10.52019014456053</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.001030039123055</v>
+        <v>-1.041636973272526</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.121014924765318</v>
+        <v>-3.360730740212973</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.291292997684671</v>
+        <v>1.15035706473765</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.1636016375704</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.2881329899047</v>
+        <v>-10.39688421608231</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9520079827052279</v>
+        <v>-0.9926149168546989</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.031597253637755</v>
+        <v>-3.27131306908541</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.344643285387747</v>
+        <v>1.203707352440727</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.164270143715894</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.26417944892875</v>
+        <v>-10.37293067510635</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9417580601693518</v>
+        <v>-0.982364994318822</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.007643712661798</v>
+        <v>-3.247359528109452</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.359683916118816</v>
+        <v>1.218747983171795</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789311112017776</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.151009827554142</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.00011951060595</v>
+        <v>-10.10887073678355</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8493944010019847</v>
+        <v>-0.8900013351514549</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.743583774339001</v>
+        <v>-2.983299589786656</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.504859562950741</v>
+        <v>1.363923630003721</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.83325274783973</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.148222793893841</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.293039887101111</v>
+        <v>-9.401791113278717</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5693495852603507</v>
+        <v>-0.6099565194098213</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.743583774339001</v>
+        <v>-2.983299589786656</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.50207252929044</v>
+        <v>1.36113659634342</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.148566417781682</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.252855588734921</v>
+        <v>-9.361606814912527</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5529322420260332</v>
+        <v>-0.5935391761755038</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.703399475972811</v>
+        <v>-2.943115291420465</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.526526732197996</v>
+        <v>1.385590799250976</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.147933239002439</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.172785793197116</v>
+        <v>-9.281537019374722</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5215375025901547</v>
+        <v>-0.5621444367396249</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.623329680435007</v>
+        <v>-2.863045495882661</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.573935430741436</v>
+        <v>1.432999497794415</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.155857667840292</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.939304570967519</v>
+        <v>-9.048055797145125</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4202205848604632</v>
+        <v>-0.4608275190099334</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.389848458205408</v>
+        <v>-2.629564273653063</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.721948592917047</v>
+        <v>1.581012659970026</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801637122785792</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.759596040823645</v>
+        <v>-8.868347267001251</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3512293831158728</v>
+        <v>-0.3918363172653434</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.332676954042712</v>
+        <v>-2.572392769490367</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.753359285101705</v>
+        <v>1.612423352154685</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763182248390432</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.627320567192758</v>
+        <v>-8.736071793370364</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3029517069164909</v>
+        <v>-0.3435586410659615</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.200401480411826</v>
+        <v>-2.44011729585948</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.828092056027264</v>
+        <v>1.687156123080244</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784718794105957</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.436720892519604</v>
+        <v>-8.54547211869721</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2238967763595929</v>
+        <v>-0.2645037105090631</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.009801805738673</v>
+        <v>-2.249517621186328</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.945266921518793</v>
+        <v>1.804330988571772</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.187721093836023</v>
+        <v>-8.296472320013629</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1113905156625017</v>
+        <v>-0.1519974498119718</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.009801805738673</v>
+        <v>-2.249517621186328</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.958173262742451</v>
+        <v>1.817237329795431</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692931855607649</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.293311083609128</v>
+        <v>-8.402062309786734</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2816024411709623</v>
+        <v>-0.3222093753204325</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.115391795511777</v>
+        <v>-2.355107610959432</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.76684333927937</v>
+        <v>1.62590740633235</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770422583987907</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.312045985727725</v>
+        <v>-8.420797211905331</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2405520601413147</v>
+        <v>-0.2811589942907848</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.115391795511777</v>
+        <v>-2.355107610959432</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.815387681156457</v>
+        <v>1.674451748209436</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.164105944320125</v>
+        <v>-8.272857170497732</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3012549662664425</v>
+        <v>-0.3418619004159127</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.09507087960322</v>
+        <v>-2.334786695050874</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.707701308013424</v>
+        <v>1.566765375066403</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.037213537885055</v>
+        <v>-8.145964764062661</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2592119899458925</v>
+        <v>-0.299818924095363</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.96817847316815</v>
+        <v>-2.207894288615805</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.775122765620987</v>
+        <v>1.634186832673967</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.993665131114365</v>
+        <v>-8.10241635729197</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2487532393327094</v>
+        <v>-0.2893601734821796</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.96817847316815</v>
+        <v>-2.207894288615805</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.768162153525894</v>
+        <v>1.627226220578873</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.751516737660507</v>
+        <v>-7.860267963838112</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1374315275700231</v>
+        <v>-0.1780384617194932</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.96817847316815</v>
+        <v>-2.207894288615805</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.782624507907037</v>
+        <v>1.641688574960017</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.688287365892158</v>
+        <v>-7.797038592069764</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1176076584034886</v>
+        <v>-0.1582145925529588</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.96817847316815</v>
+        <v>-2.207894288615805</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.777156628366232</v>
+        <v>1.636220695419212</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.501799673515152</v>
+        <v>-7.610550899692758</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.04551448744210962</v>
+        <v>-0.08612142159157932</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.781690780791144</v>
+        <v>-2.021406596238798</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.886547337803013</v>
+        <v>1.745611404855992</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812453678919911</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.480650474611709</v>
+        <v>-7.589401700789314</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02935382964340683</v>
+        <v>-0.06996076379287697</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.7605415818877</v>
+        <v>-2.000257397335355</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.906937835382404</v>
+        <v>1.766001902435383</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.236885032628265</v>
+        <v>-7.34563625880587</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.06393305549702122</v>
+        <v>0.02332612134755152</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.7605415818877</v>
+        <v>-2.000257397335355</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.902718543729455</v>
+        <v>1.761782610782434</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.972856965435005</v>
+        <v>-7.081608191612609</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1716685962943414</v>
+        <v>0.1310616621448717</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.558676183071747</v>
+        <v>-1.798391998519401</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.025962096939043</v>
+        <v>1.885026163992022</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.72300657148593</v>
+        <v>-6.831757797663535</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.264350828857673</v>
+        <v>0.2237438947082038</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.558676183071747</v>
+        <v>-1.798391998519401</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.018704171922745</v>
+        <v>1.877768238975724</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.419439082481952</v>
+        <v>-6.528190308659556</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3893769479799136</v>
+        <v>0.3487700138304439</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.558676183071747</v>
+        <v>-1.798391998519401</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.022303295443394</v>
+        <v>1.881367362496373</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.78093391139299</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.345959173629938</v>
+        <v>-6.454710399807542</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4320964175752726</v>
+        <v>0.3914894834258029</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.485196274219732</v>
+        <v>-1.724912089667387</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.079718746809156</v>
+        <v>1.938782813862136</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773765222632784</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.120926173961115</v>
+        <v>-6.229677400138719</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5211300950590987</v>
+        <v>0.4805231609096294</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.260163274550909</v>
+        <v>-1.499879089998564</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.213759024226747</v>
+        <v>2.072823091279726</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.906291796324708</v>
+        <v>-6.015043022502312</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6116786471679792</v>
+        <v>0.5710717130185095</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.045528896914503</v>
+        <v>-1.285244712362157</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.347234451862908</v>
+        <v>2.206298518915887</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.639691439350356</v>
+        <v>-5.748442665527961</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6995130487415153</v>
+        <v>0.6589061145920456</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.045528896914503</v>
+        <v>-1.285244712362157</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.328428710646704</v>
+        <v>2.187492777699683</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.399260942545496</v>
+        <v>-5.5080121687231</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7974283240883366</v>
+        <v>0.7568213899388674</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8050984001096424</v>
+        <v>-1.044814215557297</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.474430085354497</v>
+        <v>2.333494152407477</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.15647013489605</v>
+        <v>-5.265221361073655</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8984739609829351</v>
+        <v>0.8578670268334654</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8050984001096424</v>
+        <v>-1.044814215557297</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.478359399189317</v>
+        <v>2.337423466242297</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822326997879969</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.040530285270865</v>
+        <v>-5.14928151144847</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9455284847503491</v>
+        <v>0.9049215506008799</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7282766690935185</v>
+        <v>-0.9679924845411731</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.525131021716332</v>
+        <v>2.384195088769311</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848616626502342</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.797874696847702</v>
+        <v>-4.906625923025306</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.039588791339608</v>
+        <v>0.9989818571901385</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7282766690935185</v>
+        <v>-0.9679924845411731</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.522129092936325</v>
+        <v>2.381193159989305</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.577853898810691</v>
+        <v>-4.686605124988295</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.129176147565027</v>
+        <v>1.088569213415557</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5870568240255383</v>
+        <v>-0.8267726394731929</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.608440036987727</v>
+        <v>2.467504104040707</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.378605268905882</v>
+        <v>-4.487356495083486</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.224769782328774</v>
+        <v>1.184162848179304</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5870568240255383</v>
+        <v>-0.8267726394731929</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.624334219789551</v>
+        <v>2.48339828684253</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.32037636426459</v>
+        <v>-4.327841391564117</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.249207188625592</v>
+        <v>1.249114734027354</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5288279193842461</v>
+        <v>-0.667257535953823</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.660417407014628</v>
+        <v>2.580253193394454</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.175704219164852</v>
+        <v>-4.183169246464379</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.317164149226927</v>
+        <v>1.317071694628689</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3841557742845087</v>
+        <v>-0.5225853908540856</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.75730879663591</v>
+        <v>2.677144583015736</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.903141953293337</v>
+        <v>2.906035509614909</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.157934760233896</v>
+        <v>-4.165399787533423</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.239611624886031</v>
+        <v>1.239519170287793</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3663863153535531</v>
+        <v>-0.50481593192313</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.683310164081205</v>
+        <v>2.603145950461031</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762647477674519</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.925542446615903</v>
+        <v>2.928436002937475</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.071135262454888</v>
+        <v>-4.078600289754414</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.296731917320201</v>
+        <v>1.296639462721962</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3663863153535531</v>
+        <v>-0.50481593192313</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.705710657403771</v>
+        <v>2.625546443783597</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.925614847989315</v>
+        <v>2.928508404310887</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.971442647725876</v>
+        <v>-3.978907675025402</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.336681364585217</v>
+        <v>1.336588909986979</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2666937006245414</v>
+        <v>-0.4051233171941183</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.765598627614591</v>
+        <v>2.685434413994416</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.936621770464017</v>
+        <v>2.939515326785589</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.039812834049886</v>
+        <v>-4.047277861349412</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.320340212530315</v>
+        <v>1.320247757932077</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2574180015883265</v>
+        <v>-0.3958476181579033</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.782170969511021</v>
+        <v>2.702006755890848</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.927058479095908</v>
+        <v>2.929952035417481</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.91839640442341</v>
+        <v>-3.925861431722936</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.359343493012797</v>
+        <v>1.359251038414559</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2574180015883265</v>
+        <v>-0.3958476181579033</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.772607678142913</v>
+        <v>2.692443464522739</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.751768044136295</v>
+        <v>2.754661600457867</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.949389563752115</v>
+        <v>-3.956854591051641</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.171655794321702</v>
+        <v>1.171563339723464</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2574180015883265</v>
+        <v>-0.3958476181579033</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.5973172431833</v>
+        <v>2.517153029563126</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.746042526205904</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.756335276128083</v>
+        <v>2.759228832449655</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.773915303959646</v>
+        <v>-3.781380331259172</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.246412730230477</v>
+        <v>1.246320275632239</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2574180015883265</v>
+        <v>-0.3958476181579033</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.601884475175087</v>
+        <v>2.521720261554913</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.76502432322545</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.756346750014881</v>
+        <v>2.759240306336453</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.884851556600895</v>
+        <v>-3.892316583900421</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202049703060776</v>
+        <v>1.201957248462537</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2574180015883265</v>
+        <v>-0.3958476181579033</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.601895949061885</v>
+        <v>2.521731735441711</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.766834665129649</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.759478135234786</v>
+        <v>2.762371691556358</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.087878134144128</v>
+        <v>-4.095343161443654</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.123970457263388</v>
+        <v>1.12387800266515</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4604445791315598</v>
+        <v>-0.5988741957011368</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.48321138775585</v>
+        <v>2.403047174135676</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.566529876865731</v>
+        <v>3.860281407784774</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.739074085594588</v>
+        <v>2.760482983162068</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.087878134144128</v>
+        <v>-4.228593746392784</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.123970457263388</v>
+        <v>1.068689060291207</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4604445791315598</v>
+        <v>-0.5988741957011368</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.732137882580956</v>
+        <v>2.753546780148436</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240422.xlsx
+++ b/tame_output/ON/bt/strategyON_20240422.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>48.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-36.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.9%</t>
+          <t>116.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.2%</t>
+          <t>135.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-696.2%</t>
+          <t>-680.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-56.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>548.5%</t>
+          <t>788.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-584.4%</t>
+          <t>-574.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.8%</t>
+          <t>-268.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-43.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-269.4%</t>
+          <t>-266.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.1%</t>
+          <t>-159.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-283.9%</t>
+          <t>-274.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.7%</t>
+          <t>-201.7%</t>
         </is>
       </c>
     </row>
@@ -43641,10 +43641,10 @@
         <v>3.127238527942291</v>
       </c>
       <c r="D1830" t="n">
-        <v>1.400718067685997</v>
+        <v>1.26606255345954</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.687169330702942</v>
+        <v>3.633307125012359</v>
       </c>
       <c r="F1830" t="n">
         <v>2.239927473767815</v>
@@ -43664,10 +43664,10 @@
         <v>3.12760327346781</v>
       </c>
       <c r="D1831" t="n">
-        <v>1.381666322676527</v>
+        <v>1.24701080845007</v>
       </c>
       <c r="E1831" t="n">
-        <v>3.679913378224673</v>
+        <v>3.62605117253409</v>
       </c>
       <c r="F1831" t="n">
         <v>2.220875728758345</v>
@@ -43687,10 +43687,10 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.37706630313218</v>
+        <v>1.242410788905723</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.680539376029633</v>
+        <v>3.62667717033905</v>
       </c>
       <c r="F1832" t="n">
         <v>2.216275709213999</v>
@@ -43710,10 +43710,10 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.329227940885981</v>
+        <v>1.194572426659524</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.658276085032866</v>
+        <v>3.604413879342283</v>
       </c>
       <c r="F1833" t="n">
         <v>2.216275709213999</v>
@@ -43733,10 +43733,10 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.9932849733776514</v>
+        <v>0.858629459151194</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.536875507312923</v>
+        <v>3.483013301622341</v>
       </c>
       <c r="F1834" t="n">
         <v>1.880332741705669</v>
@@ -43750,16 +43750,16 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.9927331735358391</v>
+        <v>0.8580776593093818</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.534912623238543</v>
+        <v>3.48105041754796</v>
       </c>
       <c r="F1835" t="n">
         <v>1.881174505190975</v>
@@ -43779,10 +43779,10 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.8870462855935395</v>
+        <v>0.7523907713670821</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.47246314068907</v>
+        <v>3.418600934998487</v>
       </c>
       <c r="F1836" t="n">
         <v>1.866613431488292</v>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7050397222705709</v>
+        <v>0.5703842080441135</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.400149654085757</v>
+        <v>3.346287448395174</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43819,16 +43819,16 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.6568174554234874</v>
+        <v>0.52216194119703</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.38494072996859</v>
+        <v>3.331078524278007</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4196859635736923</v>
+        <v>0.2850304493472349</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.325029217726214</v>
+        <v>3.271167012035631</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4247235543012788</v>
+        <v>0.2900680400748214</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.325621694202586</v>
+        <v>3.271759488512004</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.2620974743366402</v>
+        <v>0.1274419601101828</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.239317643840468</v>
+        <v>3.185455438149885</v>
       </c>
       <c r="F1841" t="n">
         <v>1.711409540942887</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.1963300842872281</v>
+        <v>0.06167457006077076</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.214028296951174</v>
+        <v>3.160166091260591</v>
       </c>
       <c r="F1842" t="n">
         <v>1.711409540942887</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.1827946005105185</v>
+        <v>0.04813908628406116</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.199242135428245</v>
+        <v>3.145379929737663</v>
       </c>
       <c r="F1843" t="n">
         <v>1.711409540942887</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.1010227000827669</v>
+        <v>-0.03363281414369051</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.156616101212383</v>
+        <v>3.1027538955218</v>
       </c>
       <c r="F1844" t="n">
         <v>1.738445114349024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.0338135922108892</v>
+        <v>-0.1008419220155682</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.134497774897334</v>
+        <v>3.080635569206751</v>
       </c>
       <c r="F1845" t="n">
         <v>1.738445114349024</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.1737521921807227</v>
+        <v>-0.3084077064071801</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.04929625725993</v>
+        <v>2.995434051569347</v>
       </c>
       <c r="F1846" t="n">
         <v>1.530879329957412</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.5915062157275597</v>
+        <v>-0.7261617299540171</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.880121539346258</v>
+        <v>2.826259333655675</v>
       </c>
       <c r="F1847" t="n">
         <v>1.113125306410575</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.8131281492856772</v>
+        <v>-0.9477836635121346</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.791338982521933</v>
+        <v>2.73747677683135</v>
       </c>
       <c r="F1848" t="n">
         <v>1.075599172723206</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.021132207638755</v>
+        <v>-1.155787721865212</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.713029503734627</v>
+        <v>2.659167298044044</v>
       </c>
       <c r="F1849" t="n">
         <v>1.075599172723206</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.23254462852673</v>
+        <v>-1.367200142753187</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.623545991717426</v>
+        <v>2.569683786026842</v>
       </c>
       <c r="F1850" t="n">
         <v>0.8641867518352306</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.571703006115252</v>
+        <v>-1.706358520341709</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.480966939988466</v>
+        <v>2.427104734297883</v>
       </c>
       <c r="F1851" t="n">
         <v>0.5250283742467086</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.899720227842731</v>
+        <v>-2.034375742069188</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.370098341036242</v>
+        <v>2.316236135345659</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1970111525192294</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.393045099377909</v>
+        <v>-2.527700613604366</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.180867142830739</v>
+        <v>2.127004937140156</v>
       </c>
       <c r="F1853" t="n">
         <v>0.09202503827961067</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.885430127402006</v>
+        <v>-3.020085641628463</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.985019523664833</v>
+        <v>1.93115731797425</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4003599897444861</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.270610518332079</v>
+        <v>-3.405266032558536</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.829489906105667</v>
+        <v>1.775627700415084</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4003599897444861</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.614293291558742</v>
+        <v>-3.748948805785199</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.693785920269618</v>
+        <v>1.639923714579035</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5082660417717042</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.97194364179709</v>
+        <v>-4.106599156023547</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.546831838830537</v>
+        <v>1.492969633139954</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.8659163920100523</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.281177744793141</v>
+        <v>-4.415833259019598</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.424911124332376</v>
+        <v>1.371048918641793</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.8659163920100523</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.712983537942928</v>
+        <v>-4.847639052169385</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.238521694539865</v>
+        <v>1.184659488849283</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.002333888451319</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.94767753207548</v>
+        <v>-5.082333046301938</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.132928871888935</v>
+        <v>1.079066666198352</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.9959976212220641</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.283340179305933</v>
+        <v>-5.41799569353239</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9972444046527191</v>
+        <v>0.9433821989621363</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.9959976212220641</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.646966424206246</v>
+        <v>-5.781621938432703</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8582814669268357</v>
+        <v>0.8044192612362524</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.09421925808919</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.012093806844993</v>
+        <v>-6.14674932107145</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7114850288771684</v>
+        <v>0.657622823186585</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.390530042388202</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.420682584025672</v>
+        <v>-6.555338098252129</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5468110620196556</v>
+        <v>0.4929488563290727</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.799118819568881</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.833665068166765</v>
+        <v>-6.968320582393223</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3768035008346788</v>
+        <v>0.322941295144096</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.799118819568881</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.250056942453763</v>
+        <v>-7.38471245668022</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2082408017287571</v>
+        <v>0.1543785960381743</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.799118819568881</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.626733952983607</v>
+        <v>-7.761389467210065</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.06782868818549836</v>
+        <v>0.0139664824949155</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.799118819568881</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.972608774968416</v>
+        <v>-8.107264289194873</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.07442167546272982</v>
+        <v>-0.1282838811533127</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.799118819568881</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.134751045431509</v>
+        <v>-8.269406559657966</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1408736635929659</v>
+        <v>-0.1947358692835492</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.799118819568881</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.431412387241707</v>
+        <v>-8.566067901468164</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.255759224387837</v>
+        <v>-0.3096214300784204</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.867861955302759</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.864761495351942</v>
+        <v>-8.9994170095784</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4331251721663345</v>
+        <v>-0.4869873778569174</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.867861955302759</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.247762884094573</v>
+        <v>-9.382418398321031</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5864278289849709</v>
+        <v>-0.6402900346755538</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.867861955302759</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.405161764307694</v>
+        <v>-9.539817278534152</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6468158650987892</v>
+        <v>-0.7006780707893721</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.02526083551588</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.764692086811696</v>
+        <v>-9.899347601038153</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7852776908023396</v>
+        <v>-0.8391398964929224</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.02526083551588</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.09109211547671</v>
+        <v>-10.22574762970317</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9079216823111671</v>
+        <v>-0.9617838880017504</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.351660864180893</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.500446096776675</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.31024108355091</v>
+        <v>-10.44489659777736</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9925395189190778</v>
+        <v>-1.04640172460966</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.570809832255091</v>
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.41235234558823</v>
+        <v>-10.44120567282095</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.030490467412433</v>
+        <v>-1.044925354627096</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.672921094292411</v>
+        <v>-2.570809832255091</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.531054238561158</v>
+        <v>1.589427439461978</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.61661052091809</v>
+        <v>-10.58950687308045</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.106680540425737</v>
+        <v>-1.098732637612251</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.8005600389064</v>
+        <v>-2.708948081406872</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.459984068911407</v>
+        <v>1.512057687089552</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.83464829254927</v>
+        <v>-10.80754464471162</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.189413094593772</v>
+        <v>-1.181465191780287</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.975330807002299</v>
+        <v>-2.883718849502771</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.359604162538304</v>
+        <v>1.411677780716449</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.76117846088182</v>
+        <v>-10.73407481304418</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.14465346043337</v>
+        <v>-1.136705557619885</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.901860975334851</v>
+        <v>-2.810249017835322</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.419057763032194</v>
+        <v>1.471131381210339</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.93630287826836</v>
+        <v>-10.90919923043072</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.200148006640472</v>
+        <v>-1.192200103826986</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.076985392721395</v>
+        <v>-2.985373435221866</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.328538333347784</v>
+        <v>1.380611951525929</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.17075497228285</v>
+        <v>-11.14365132444521</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.301148009147863</v>
+        <v>-1.293200106334378</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.076985392721395</v>
+        <v>-2.985373435221866</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.321319168446188</v>
+        <v>1.373392786624333</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.45855881682009</v>
+        <v>-11.43145516898245</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.422941737736735</v>
+        <v>-1.41499383492325</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.364789237258633</v>
+        <v>-3.273177279759104</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.14196467094987</v>
+        <v>1.194038289128014</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.68838326398392</v>
+        <v>-11.66127961614627</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.513755726763709</v>
+        <v>-1.505807823950224</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.527436774328793</v>
+        <v>-3.435824816829265</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.045491938546329</v>
+        <v>1.097565556724474</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.92041218372018</v>
+        <v>-11.89330853588253</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.603873566029099</v>
+        <v>-1.595925663215614</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.589449471517216</v>
+        <v>-3.497837514017688</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.01097804886239</v>
+        <v>1.063051667040535</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.86839666975136</v>
+        <v>-11.84129302191372</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.579077024755173</v>
+        <v>-1.571129121941687</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.589449471517216</v>
+        <v>-3.497837514017688</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.014968384548791</v>
+        <v>1.067042002726936</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.01006851147548</v>
+        <v>-11.98296486363784</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.637220988343563</v>
+        <v>-1.629273085530077</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.589449471517216</v>
+        <v>-3.497837514017688</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.013493157650049</v>
+        <v>1.065566775828194</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.10897525193476</v>
+        <v>-12.08187160409712</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.6617302743624</v>
+        <v>-1.653782371548915</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.688356211976492</v>
+        <v>-3.596744254476964</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9692025235393564</v>
+        <v>1.021276141717501</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.90982314469766</v>
+        <v>-11.88271949686002</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.595120565114243</v>
+        <v>-1.587172662300758</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.523033686026678</v>
+        <v>-3.43142172852715</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.055344905462562</v>
+        <v>1.107418523640706</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.68397799197825</v>
+        <v>-11.65687434414061</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.495203430990271</v>
+        <v>-1.487255528176786</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.481107010439515</v>
+        <v>-3.389495052939987</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.090079983851068</v>
+        <v>1.142153602029213</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.39770317965555</v>
+        <v>-11.37059953181791</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.379554361505134</v>
+        <v>-1.371606458691649</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.481107010439515</v>
+        <v>-3.389495052939987</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.091219128407127</v>
+        <v>1.143292746585272</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.710931958116211</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.45059846769984</v>
+        <v>-11.4234948198622</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.39807870256074</v>
+        <v>-1.390130799747256</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.476151664351069</v>
+        <v>-3.384539706851541</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.096826110222302</v>
+        <v>1.148899728400447</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768948099081562</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.16668973677109</v>
+        <v>-11.13958608893345</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.278781505950604</v>
+        <v>-1.270833603137119</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.476151664351069</v>
+        <v>-3.384539706851541</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.102559814460939</v>
+        <v>1.154633432639084</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728574354425322</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.051268812633</v>
+        <v>-11.02416516479535</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.242350398689231</v>
+        <v>-1.234402495875747</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.360730740212973</v>
+        <v>-3.269118782713445</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.162075106549931</v>
+        <v>1.214148724728076</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747699084702406</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.78743194542893</v>
+        <v>-10.76032829759128</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.146699133120511</v>
+        <v>-1.138751230307026</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.360730740212973</v>
+        <v>-3.269118782713445</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.152191625237024</v>
+        <v>1.204265243415168</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766313503906222</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.52019014456053</v>
+        <v>-10.49308649672289</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.041636973272526</v>
+        <v>-1.033689070459041</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.360730740212973</v>
+        <v>-3.269118782713445</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.15035706473765</v>
+        <v>1.202430682915795</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.39688421608231</v>
+        <v>-10.36978056824467</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9926149168546989</v>
+        <v>-0.9846670140412139</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.27131306908541</v>
+        <v>-3.179701111585882</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.203707352440727</v>
+        <v>1.255780970618872</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097246</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.37293067510635</v>
+        <v>-10.34582702726871</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.982364994318822</v>
+        <v>-0.974417091505337</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.247359528109452</v>
+        <v>-3.155747570609925</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.218747983171795</v>
+        <v>1.27082160134994</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017776</v>
+        <v>3.789307536487768</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.10887073678355</v>
+        <v>-10.08176708894591</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8900013351514549</v>
+        <v>-0.8820534323379707</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.983299589786656</v>
+        <v>-2.891687632287128</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.363923630003721</v>
+        <v>1.415997248181865</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783973</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.401791113278717</v>
+        <v>-9.374687465441076</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6099565194098213</v>
+        <v>-0.6020086165963368</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.983299589786656</v>
+        <v>-2.891687632287128</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.36113659634342</v>
+        <v>1.413210214521564</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.361606814912527</v>
+        <v>-9.334503167074885</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5935391761755038</v>
+        <v>-0.5855912733620192</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.943115291420465</v>
+        <v>-2.851503333920937</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.385590799250976</v>
+        <v>1.43766441742912</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.281537019374722</v>
+        <v>-9.254433371537081</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5621444367396249</v>
+        <v>-0.5541965339261403</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.863045495882661</v>
+        <v>-2.771433538383133</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.432999497794415</v>
+        <v>1.48507311597256</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787326853761804</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.048055797145125</v>
+        <v>-9.020952149307483</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4608275190099334</v>
+        <v>-0.4528796161964488</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.629564273653063</v>
+        <v>-2.537952316153535</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.581012659970026</v>
+        <v>1.633086278148171</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785792</v>
+        <v>3.801633547255781</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.034058973264847</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.868347267001251</v>
+        <v>-8.84124361916361</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3918363172653434</v>
+        <v>-0.502794898714344</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.572392769490367</v>
+        <v>-2.480780811990839</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.612423352154685</v>
+        <v>1.545590486070344</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390432</v>
+        <v>3.763178672860422</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.029426460011874</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.736071793370364</v>
+        <v>-8.708968145532722</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3435586410659615</v>
+        <v>-0.4545172225149621</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.44011729585948</v>
+        <v>-2.348505338359952</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.687156123080244</v>
+        <v>1.620323256995903</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105957</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.032241520699511</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.54547211869721</v>
+        <v>-8.518368470859569</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2645037105090631</v>
+        <v>-0.3754622919580637</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.249517621186328</v>
+        <v>-2.1579056636868</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.804330988571772</v>
+        <v>1.737498122487432</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.04514786192317</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.296472320013629</v>
+        <v>-8.269368672175988</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1519974498119718</v>
+        <v>-0.2629560312609729</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.249517621186328</v>
+        <v>-2.1579056636868</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.817237329795431</v>
+        <v>1.75040446371109</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607649</v>
+        <v>3.692928280077639</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.917171932323951</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.402062309786734</v>
+        <v>-8.374958661949092</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3222093753204325</v>
+        <v>-0.4331679567694331</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.355107610959432</v>
+        <v>-2.263495653459904</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.62590740633235</v>
+        <v>1.559074540248009</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987907</v>
+        <v>3.770419008457896</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>2.965716274201037</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.420797211905331</v>
+        <v>-8.393693564067689</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2811589942907848</v>
+        <v>-0.3921175757397855</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.355107610959432</v>
+        <v>-2.263495653459904</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.674451748209436</v>
+        <v>1.607618882125095</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760330111180805</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.84583735151287</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.272857170497732</v>
+        <v>-8.24575352266009</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3418619004159127</v>
+        <v>-0.4528204818649133</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.334786695050874</v>
+        <v>-2.243174737551346</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.566765375066403</v>
+        <v>1.499932508982062</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723562653879198</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.837123365259392</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.145964764062661</v>
+        <v>-8.11886111622502</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.299818924095363</v>
+        <v>-0.4107775055443637</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.207894288615805</v>
+        <v>-2.116282331116277</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.634186832673967</v>
+        <v>1.567353966589626</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729966140568102</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.830162753164299</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.10241635729197</v>
+        <v>-8.075312709454328</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2893601734821796</v>
+        <v>-0.4003187549311802</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.207894288615805</v>
+        <v>-2.116282331116277</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.627226220578873</v>
+        <v>1.560393354494533</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782918957963413</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.844625107545442</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.860267963838112</v>
+        <v>-7.83316431600047</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1780384617194932</v>
+        <v>-0.2889970431684938</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.207894288615805</v>
+        <v>-2.116282331116277</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.641688574960017</v>
+        <v>1.574855708875676</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828547911192811</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.839157228004637</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.797038592069764</v>
+        <v>-7.769934944232122</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1582145925529588</v>
+        <v>-0.2691731740019594</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.207894288615805</v>
+        <v>-2.116282331116277</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.636220695419212</v>
+        <v>1.569387829334871</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.836655322015214</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.610550899692758</v>
+        <v>-7.583447251855116</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.08612142159157932</v>
+        <v>-0.1970800030405804</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.021406596238798</v>
+        <v>-1.92979463873927</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.745611404855992</v>
+        <v>1.678778538771652</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919911</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.844356300252539</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.589401700789314</v>
+        <v>-7.562298052951673</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.06996076379287697</v>
+        <v>-0.1809193452418776</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.000257397335355</v>
+        <v>-1.908645439835827</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.766001902435383</v>
+        <v>1.699169036351043</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.840137008599589</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.34563625880587</v>
+        <v>-7.318532610968228</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.02332612134755152</v>
+        <v>-0.08763246010144909</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.000257397335355</v>
+        <v>-1.908645439835827</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.761782610782434</v>
+        <v>1.694949744698093</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.842261322519605</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.081608191612609</v>
+        <v>-7.054504543774968</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1310616621448717</v>
+        <v>0.02010308069587108</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.798391998519401</v>
+        <v>-1.706780041019873</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.885026163992022</v>
+        <v>1.818193297907682</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.835003397503308</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.831757797663535</v>
+        <v>-6.804654149825893</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2237438947082038</v>
+        <v>0.1127853132592027</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.798391998519401</v>
+        <v>-1.706780041019873</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.877768238975724</v>
+        <v>1.810935372891384</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.838602521023956</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.528190308659556</v>
+        <v>-6.501086660821914</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3487700138304439</v>
+        <v>0.2378114323814433</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.798391998519401</v>
+        <v>-1.706780041019873</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.881367362496373</v>
+        <v>1.814534496412032</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.78093391139299</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.85193002707851</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.454710399807542</v>
+        <v>-6.427606751969901</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3914894834258029</v>
+        <v>0.2805309019768023</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.724912089667387</v>
+        <v>-1.633300132167859</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.938782813862136</v>
+        <v>1.871949947777795</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632784</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.850950504694807</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.229677400138719</v>
+        <v>-6.202573752301078</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4805231609096294</v>
+        <v>0.3695645794606284</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.499879089998564</v>
+        <v>-1.408267132499036</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.072823091279726</v>
+        <v>2.005990225195386</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883076</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.855645305749124</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.015043022502312</v>
+        <v>-5.987939374664671</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5710717130185095</v>
+        <v>0.4601131315695088</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.285244712362157</v>
+        <v>-1.193632754862629</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.206298518915887</v>
+        <v>2.139465652831547</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.83683956453292</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.748442665527961</v>
+        <v>-5.721339017690319</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6589061145920456</v>
+        <v>0.547947533143045</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.285244712362157</v>
+        <v>-1.193632754862629</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.187492777699683</v>
+        <v>2.120659911615343</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.838582641157797</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.5080121687231</v>
+        <v>-5.480908520885459</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7568213899388674</v>
+        <v>0.6458628084898663</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.044814215557297</v>
+        <v>-0.953202258057769</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.333494152407477</v>
+        <v>2.266661286323136</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.842511954992617</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.265221361073655</v>
+        <v>-5.238117713236013</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8578670268334654</v>
+        <v>0.7469084453844648</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.044814215557297</v>
+        <v>-0.953202258057769</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.337423466242297</v>
+        <v>2.270590600157957</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879969</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.843190538909957</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.14928151144847</v>
+        <v>-5.122177863610828</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9049215506008799</v>
+        <v>0.7939629691518788</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9679924845411731</v>
+        <v>-0.8763805270416452</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.384195088769311</v>
+        <v>2.317362222684971</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502342</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.840188610129951</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.906625923025306</v>
+        <v>-4.879522275187664</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9989818571901385</v>
+        <v>0.8880232757411379</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9679924845411731</v>
+        <v>-0.8763805270416452</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.381193159989305</v>
+        <v>2.314360293904964</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.841767647140565</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.686605124988295</v>
+        <v>-4.659501477150654</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.088569213415557</v>
+        <v>0.9776106319665563</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8267726394731929</v>
+        <v>-0.7351606819736649</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.467504104040707</v>
+        <v>2.400671237956367</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.857661829942388</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.487356495083486</v>
+        <v>-4.460252847245845</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.184162848179304</v>
+        <v>1.073204266730303</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8267726394731929</v>
+        <v>-0.7351606819736649</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.48339828684253</v>
+        <v>2.416565420758189</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.85880767438269</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.327841391564117</v>
+        <v>-4.300737743726475</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.249114734027354</v>
+        <v>1.138156152578353</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.667257535953823</v>
+        <v>-0.575645578454295</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.580253193394454</v>
+        <v>2.513420327310114</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.86889577694413</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.183169246464379</v>
+        <v>-4.156065598626737</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.317071694628689</v>
+        <v>1.206113113179688</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5225853908540856</v>
+        <v>-0.4309734333545576</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.677144583015736</v>
+        <v>2.610311716931396</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.906035509614909</v>
+        <v>2.784235469030852</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.165399787533423</v>
+        <v>-4.138296139695782</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.239519170287793</v>
+        <v>1.128560588838792</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.50481593192313</v>
+        <v>-0.413203974423602</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.603145950461031</v>
+        <v>2.536313084376691</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674519</v>
+        <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.928436002937475</v>
+        <v>2.806635962353418</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.078600289754414</v>
+        <v>-4.051496641916772</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.296639462721962</v>
+        <v>1.185680881272962</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.50481593192313</v>
+        <v>-0.413203974423602</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.625546443783597</v>
+        <v>2.558713577699257</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.928508404310887</v>
+        <v>2.80670836372683</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.978907675025402</v>
+        <v>-3.951804027187761</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.336588909986979</v>
+        <v>1.225630328537978</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4051233171941183</v>
+        <v>-0.3135113596945903</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.685434413994416</v>
+        <v>2.618601547910076</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.939515326785589</v>
+        <v>2.817715286201532</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.047277861349412</v>
+        <v>-4.020174213511771</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.320247757932077</v>
+        <v>1.209289176483076</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3958476181579033</v>
+        <v>-0.3042356606583753</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.702006755890848</v>
+        <v>2.635173889806507</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.929952035417481</v>
+        <v>2.808151994833423</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.925861431722936</v>
+        <v>-3.898757783885294</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.359251038414559</v>
+        <v>1.248292456965558</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3958476181579033</v>
+        <v>-0.3042356606583753</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.692443464522739</v>
+        <v>2.625610598438398</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.754661600457867</v>
+        <v>2.63286155987381</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.956854591051641</v>
+        <v>-3.929750943214</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.171563339723464</v>
+        <v>1.060604758274463</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3958476181579033</v>
+        <v>-0.3042356606583753</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.517153029563126</v>
+        <v>2.450320163478785</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205904</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.759228832449655</v>
+        <v>2.637428791865598</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.781380331259172</v>
+        <v>-3.75427668342153</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.246320275632239</v>
+        <v>1.135361694183239</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3958476181579033</v>
+        <v>-0.3042356606583753</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.521720261554913</v>
+        <v>2.454887395470573</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322545</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.759240306336453</v>
+        <v>2.637440265752395</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.892316583900421</v>
+        <v>-3.865212936062779</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.201957248462537</v>
+        <v>1.090998667013537</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3958476181579033</v>
+        <v>-0.3042356606583753</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.521731735441711</v>
+        <v>2.454898869357371</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.766834665129649</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.762371691556358</v>
+        <v>2.640571650972301</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.095343161443654</v>
+        <v>-4.068239513606012</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.12387800266515</v>
+        <v>1.012919421216149</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5988741957011368</v>
+        <v>-0.5072622382016088</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.403047174135676</v>
+        <v>2.336214308051336</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.860281407784774</v>
+        <v>3.770129107287129</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.760482983162068</v>
+        <v>2.747583308382735</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.228593746392784</v>
+        <v>-4.132257319888212</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.068689060291207</v>
+        <v>1.094323956113703</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5988741957011368</v>
+        <v>-0.5072622382016088</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.753546780148436</v>
+        <v>2.44322596546177</v>
       </c>
     </row>
   </sheetData>
